--- a/reports/daily/nikkei225_ranking_ver7_20260818.xlsx
+++ b/reports/daily/nikkei225_ranking_ver7_20260818.xlsx
@@ -860,7 +860,7 @@
         <v>1734</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -868,9 +868,15 @@
       <c r="AX2" t="n">
         <v>0</v>
       </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
+      <c r="AY2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
       <c r="BB2" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -1039,7 +1045,7 @@
         <v>2081</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -1047,9 +1053,15 @@
       <c r="AX3" t="n">
         <v>0</v>
       </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
+      <c r="AY3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
       <c r="BB3" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -1218,7 +1230,7 @@
         <v>1554</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
@@ -1226,9 +1238,15 @@
       <c r="AX4" t="n">
         <v>0</v>
       </c>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
+      <c r="AY4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
       <c r="BB4" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -1401,7 +1419,7 @@
         <v>1841.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
@@ -1409,9 +1427,15 @@
       <c r="AX5" t="n">
         <v>0</v>
       </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
+      <c r="AY5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
       <c r="BB5" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -1580,7 +1604,7 @@
         <v>1771</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
@@ -1588,9 +1612,15 @@
       <c r="AX6" t="n">
         <v>0</v>
       </c>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
+      <c r="AY6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
       <c r="BB6" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -1759,7 +1789,7 @@
         <v>7647</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
@@ -1767,9 +1797,15 @@
       <c r="AX7" t="n">
         <v>0</v>
       </c>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="inlineStr"/>
+      <c r="AY7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
       <c r="BB7" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -1938,7 +1974,7 @@
         <v>497.9</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
@@ -1946,9 +1982,15 @@
       <c r="AX8" t="n">
         <v>0</v>
       </c>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="inlineStr"/>
+      <c r="AY8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
       <c r="BB8" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -2117,7 +2159,7 @@
         <v>5495</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
@@ -2125,9 +2167,15 @@
       <c r="AX9" t="n">
         <v>0</v>
       </c>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
+      <c r="AY9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
       <c r="BB9" t="inlineStr">
         <is>
           <t>MATURE</t>
@@ -2300,7 +2348,7 @@
         <v>8531</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW10" t="n">
         <v>0</v>
@@ -2308,9 +2356,15 @@
       <c r="AX10" t="n">
         <v>0</v>
       </c>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="inlineStr"/>
+      <c r="AY10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
       <c r="BB10" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -2483,7 +2537,7 @@
         <v>3654</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW11" t="n">
         <v>0</v>
@@ -2491,9 +2545,15 @@
       <c r="AX11" t="n">
         <v>0</v>
       </c>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="inlineStr"/>
+      <c r="AY11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
       <c r="BB11" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -2662,7 +2722,7 @@
         <v>2837.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW12" t="n">
         <v>0</v>
@@ -2670,9 +2730,15 @@
       <c r="AX12" t="n">
         <v>0</v>
       </c>
-      <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr"/>
-      <c r="BA12" t="inlineStr"/>
+      <c r="AY12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
       <c r="BB12" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -2841,7 +2907,7 @@
         <v>4985</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
@@ -2849,9 +2915,15 @@
       <c r="AX13" t="n">
         <v>0</v>
       </c>
-      <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr"/>
-      <c r="BA13" t="inlineStr"/>
+      <c r="AY13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
       <c r="BB13" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -3020,7 +3092,7 @@
         <v>3000</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW14" t="n">
         <v>0</v>
@@ -3028,9 +3100,15 @@
       <c r="AX14" t="n">
         <v>0</v>
       </c>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr"/>
-      <c r="BA14" t="inlineStr"/>
+      <c r="AY14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
       <c r="BB14" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -3199,7 +3277,7 @@
         <v>4074</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
@@ -3207,9 +3285,15 @@
       <c r="AX15" t="n">
         <v>0</v>
       </c>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr"/>
-      <c r="BA15" t="inlineStr"/>
+      <c r="AY15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
       <c r="BB15" t="inlineStr">
         <is>
           <t>MATURE</t>
@@ -3378,7 +3462,7 @@
         <v>8059</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
@@ -3386,9 +3470,15 @@
       <c r="AX16" t="n">
         <v>0</v>
       </c>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr"/>
-      <c r="BA16" t="inlineStr"/>
+      <c r="AY16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
       <c r="BB16" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -3557,7 +3647,7 @@
         <v>1370.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW17" t="n">
         <v>0</v>
@@ -3565,9 +3655,15 @@
       <c r="AX17" t="n">
         <v>0</v>
       </c>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr"/>
-      <c r="BA17" t="inlineStr"/>
+      <c r="AY17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
       <c r="BB17" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -3736,7 +3832,7 @@
         <v>12040</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW18" t="n">
         <v>0</v>
@@ -3744,9 +3840,15 @@
       <c r="AX18" t="n">
         <v>0</v>
       </c>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr"/>
-      <c r="BA18" t="inlineStr"/>
+      <c r="AY18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
       <c r="BB18" t="inlineStr">
         <is>
           <t>MATURE</t>
@@ -3919,7 +4021,7 @@
         <v>6900</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW19" t="n">
         <v>0</v>
@@ -3927,9 +4029,15 @@
       <c r="AX19" t="n">
         <v>0</v>
       </c>
-      <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr"/>
-      <c r="BA19" t="inlineStr"/>
+      <c r="AY19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
       <c r="BB19" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -4098,7 +4206,7 @@
         <v>2141.5</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW20" t="n">
         <v>0</v>
@@ -4106,9 +4214,15 @@
       <c r="AX20" t="n">
         <v>0</v>
       </c>
-      <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="inlineStr"/>
-      <c r="BA20" t="inlineStr"/>
+      <c r="AY20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
       <c r="BB20" t="inlineStr">
         <is>
           <t>MATURE</t>
@@ -4271,9 +4385,15 @@
         <v>0</v>
       </c>
       <c r="AX21" t="inlineStr"/>
-      <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="inlineStr"/>
-      <c r="BA21" t="inlineStr"/>
+      <c r="AY21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
       <c r="BB21" t="inlineStr"/>
       <c r="BC21" t="inlineStr">
         <is>
@@ -4436,9 +4556,15 @@
         <v>0</v>
       </c>
       <c r="AX22" t="inlineStr"/>
-      <c r="AY22" t="inlineStr"/>
-      <c r="AZ22" t="inlineStr"/>
-      <c r="BA22" t="inlineStr"/>
+      <c r="AY22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
       <c r="BB22" t="inlineStr"/>
       <c r="BC22" t="inlineStr">
         <is>
@@ -4597,9 +4723,15 @@
         <v>0</v>
       </c>
       <c r="AX23" t="inlineStr"/>
-      <c r="AY23" t="inlineStr"/>
-      <c r="AZ23" t="inlineStr"/>
-      <c r="BA23" t="inlineStr"/>
+      <c r="AY23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
       <c r="BB23" t="inlineStr"/>
       <c r="BC23" t="inlineStr">
         <is>
@@ -4758,9 +4890,15 @@
         <v>0</v>
       </c>
       <c r="AX24" t="inlineStr"/>
-      <c r="AY24" t="inlineStr"/>
-      <c r="AZ24" t="inlineStr"/>
-      <c r="BA24" t="inlineStr"/>
+      <c r="AY24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
       <c r="BB24" t="inlineStr"/>
       <c r="BC24" t="inlineStr">
         <is>
@@ -4923,9 +5061,15 @@
         <v>0</v>
       </c>
       <c r="AX25" t="inlineStr"/>
-      <c r="AY25" t="inlineStr"/>
-      <c r="AZ25" t="inlineStr"/>
-      <c r="BA25" t="inlineStr"/>
+      <c r="AY25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
       <c r="BB25" t="inlineStr"/>
       <c r="BC25" t="inlineStr">
         <is>
@@ -5084,9 +5228,15 @@
         <v>0</v>
       </c>
       <c r="AX26" t="inlineStr"/>
-      <c r="AY26" t="inlineStr"/>
-      <c r="AZ26" t="inlineStr"/>
-      <c r="BA26" t="inlineStr"/>
+      <c r="AY26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
       <c r="BB26" t="inlineStr"/>
       <c r="BC26" t="inlineStr">
         <is>
@@ -5245,9 +5395,15 @@
         <v>0</v>
       </c>
       <c r="AX27" t="inlineStr"/>
-      <c r="AY27" t="inlineStr"/>
-      <c r="AZ27" t="inlineStr"/>
-      <c r="BA27" t="inlineStr"/>
+      <c r="AY27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
       <c r="BB27" t="inlineStr"/>
       <c r="BC27" t="inlineStr">
         <is>
@@ -5410,9 +5566,15 @@
         <v>0</v>
       </c>
       <c r="AX28" t="inlineStr"/>
-      <c r="AY28" t="inlineStr"/>
-      <c r="AZ28" t="inlineStr"/>
-      <c r="BA28" t="inlineStr"/>
+      <c r="AY28" t="n">
+        <v>27</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
       <c r="BB28" t="inlineStr"/>
       <c r="BC28" t="inlineStr">
         <is>
@@ -5575,9 +5737,15 @@
         <v>0</v>
       </c>
       <c r="AX29" t="inlineStr"/>
-      <c r="AY29" t="inlineStr"/>
-      <c r="AZ29" t="inlineStr"/>
-      <c r="BA29" t="inlineStr"/>
+      <c r="AY29" t="n">
+        <v>28</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
       <c r="BB29" t="inlineStr"/>
       <c r="BC29" t="inlineStr">
         <is>
@@ -5740,9 +5908,15 @@
         <v>0</v>
       </c>
       <c r="AX30" t="inlineStr"/>
-      <c r="AY30" t="inlineStr"/>
-      <c r="AZ30" t="inlineStr"/>
-      <c r="BA30" t="inlineStr"/>
+      <c r="AY30" t="n">
+        <v>29</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
       <c r="BB30" t="inlineStr"/>
       <c r="BC30" t="inlineStr">
         <is>
@@ -5901,9 +6075,15 @@
         <v>0</v>
       </c>
       <c r="AX31" t="inlineStr"/>
-      <c r="AY31" t="inlineStr"/>
-      <c r="AZ31" t="inlineStr"/>
-      <c r="BA31" t="inlineStr"/>
+      <c r="AY31" t="n">
+        <v>30</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
       <c r="BB31" t="inlineStr"/>
       <c r="BC31" t="inlineStr">
         <is>
@@ -6062,9 +6242,15 @@
         <v>0</v>
       </c>
       <c r="AX32" t="inlineStr"/>
-      <c r="AY32" t="inlineStr"/>
-      <c r="AZ32" t="inlineStr"/>
-      <c r="BA32" t="inlineStr"/>
+      <c r="AY32" t="n">
+        <v>31</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
       <c r="BB32" t="inlineStr"/>
       <c r="BC32" t="inlineStr">
         <is>
@@ -6223,9 +6409,15 @@
         <v>0</v>
       </c>
       <c r="AX33" t="inlineStr"/>
-      <c r="AY33" t="inlineStr"/>
-      <c r="AZ33" t="inlineStr"/>
-      <c r="BA33" t="inlineStr"/>
+      <c r="AY33" t="n">
+        <v>32</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
       <c r="BB33" t="inlineStr"/>
       <c r="BC33" t="inlineStr">
         <is>
@@ -6384,9 +6576,15 @@
         <v>0</v>
       </c>
       <c r="AX34" t="inlineStr"/>
-      <c r="AY34" t="inlineStr"/>
-      <c r="AZ34" t="inlineStr"/>
-      <c r="BA34" t="inlineStr"/>
+      <c r="AY34" t="n">
+        <v>33</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
       <c r="BB34" t="inlineStr"/>
       <c r="BC34" t="inlineStr">
         <is>
@@ -6545,9 +6743,15 @@
         <v>0</v>
       </c>
       <c r="AX35" t="inlineStr"/>
-      <c r="AY35" t="inlineStr"/>
-      <c r="AZ35" t="inlineStr"/>
-      <c r="BA35" t="inlineStr"/>
+      <c r="AY35" t="n">
+        <v>34</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
       <c r="BB35" t="inlineStr"/>
       <c r="BC35" t="inlineStr">
         <is>
@@ -6706,9 +6910,15 @@
         <v>0</v>
       </c>
       <c r="AX36" t="inlineStr"/>
-      <c r="AY36" t="inlineStr"/>
-      <c r="AZ36" t="inlineStr"/>
-      <c r="BA36" t="inlineStr"/>
+      <c r="AY36" t="n">
+        <v>35</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
       <c r="BB36" t="inlineStr"/>
       <c r="BC36" t="inlineStr">
         <is>
@@ -6867,9 +7077,15 @@
         <v>0</v>
       </c>
       <c r="AX37" t="inlineStr"/>
-      <c r="AY37" t="inlineStr"/>
-      <c r="AZ37" t="inlineStr"/>
-      <c r="BA37" t="inlineStr"/>
+      <c r="AY37" t="n">
+        <v>36</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
       <c r="BB37" t="inlineStr"/>
       <c r="BC37" t="inlineStr">
         <is>
@@ -7028,9 +7244,15 @@
         <v>0</v>
       </c>
       <c r="AX38" t="inlineStr"/>
-      <c r="AY38" t="inlineStr"/>
-      <c r="AZ38" t="inlineStr"/>
-      <c r="BA38" t="inlineStr"/>
+      <c r="AY38" t="n">
+        <v>37</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0</v>
+      </c>
       <c r="BB38" t="inlineStr"/>
       <c r="BC38" t="inlineStr">
         <is>
@@ -7193,9 +7415,15 @@
         <v>0</v>
       </c>
       <c r="AX39" t="inlineStr"/>
-      <c r="AY39" t="inlineStr"/>
-      <c r="AZ39" t="inlineStr"/>
-      <c r="BA39" t="inlineStr"/>
+      <c r="AY39" t="n">
+        <v>38</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0</v>
+      </c>
       <c r="BB39" t="inlineStr"/>
       <c r="BC39" t="inlineStr">
         <is>
@@ -7354,9 +7582,15 @@
         <v>0</v>
       </c>
       <c r="AX40" t="inlineStr"/>
-      <c r="AY40" t="inlineStr"/>
-      <c r="AZ40" t="inlineStr"/>
-      <c r="BA40" t="inlineStr"/>
+      <c r="AY40" t="n">
+        <v>39</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0</v>
+      </c>
       <c r="BB40" t="inlineStr"/>
       <c r="BC40" t="inlineStr">
         <is>
@@ -7515,9 +7749,15 @@
         <v>0</v>
       </c>
       <c r="AX41" t="inlineStr"/>
-      <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr"/>
-      <c r="BA41" t="inlineStr"/>
+      <c r="AY41" t="n">
+        <v>40</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>0</v>
+      </c>
       <c r="BB41" t="inlineStr"/>
       <c r="BC41" t="inlineStr">
         <is>
@@ -7676,9 +7916,15 @@
         <v>0</v>
       </c>
       <c r="AX42" t="inlineStr"/>
-      <c r="AY42" t="inlineStr"/>
-      <c r="AZ42" t="inlineStr"/>
-      <c r="BA42" t="inlineStr"/>
+      <c r="AY42" t="n">
+        <v>41</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0</v>
+      </c>
       <c r="BB42" t="inlineStr"/>
       <c r="BC42" t="inlineStr">
         <is>
@@ -7837,9 +8083,15 @@
         <v>0</v>
       </c>
       <c r="AX43" t="inlineStr"/>
-      <c r="AY43" t="inlineStr"/>
-      <c r="AZ43" t="inlineStr"/>
-      <c r="BA43" t="inlineStr"/>
+      <c r="AY43" t="n">
+        <v>42</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>0</v>
+      </c>
       <c r="BB43" t="inlineStr"/>
       <c r="BC43" t="inlineStr">
         <is>
@@ -7998,9 +8250,15 @@
         <v>0</v>
       </c>
       <c r="AX44" t="inlineStr"/>
-      <c r="AY44" t="inlineStr"/>
-      <c r="AZ44" t="inlineStr"/>
-      <c r="BA44" t="inlineStr"/>
+      <c r="AY44" t="n">
+        <v>43</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>0</v>
+      </c>
       <c r="BB44" t="inlineStr"/>
       <c r="BC44" t="inlineStr">
         <is>
@@ -8159,9 +8417,15 @@
         <v>0</v>
       </c>
       <c r="AX45" t="inlineStr"/>
-      <c r="AY45" t="inlineStr"/>
-      <c r="AZ45" t="inlineStr"/>
-      <c r="BA45" t="inlineStr"/>
+      <c r="AY45" t="n">
+        <v>44</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>0</v>
+      </c>
       <c r="BB45" t="inlineStr"/>
       <c r="BC45" t="inlineStr">
         <is>
@@ -8318,9 +8582,15 @@
         <v>0</v>
       </c>
       <c r="AX46" t="inlineStr"/>
-      <c r="AY46" t="inlineStr"/>
-      <c r="AZ46" t="inlineStr"/>
-      <c r="BA46" t="inlineStr"/>
+      <c r="AY46" t="n">
+        <v>45</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>0</v>
+      </c>
       <c r="BB46" t="inlineStr"/>
       <c r="BC46" t="inlineStr">
         <is>
@@ -8479,9 +8749,15 @@
         <v>0</v>
       </c>
       <c r="AX47" t="inlineStr"/>
-      <c r="AY47" t="inlineStr"/>
-      <c r="AZ47" t="inlineStr"/>
-      <c r="BA47" t="inlineStr"/>
+      <c r="AY47" t="n">
+        <v>46</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>0</v>
+      </c>
       <c r="BB47" t="inlineStr"/>
       <c r="BC47" t="inlineStr">
         <is>
@@ -8644,9 +8920,15 @@
         <v>0</v>
       </c>
       <c r="AX48" t="inlineStr"/>
-      <c r="AY48" t="inlineStr"/>
-      <c r="AZ48" t="inlineStr"/>
-      <c r="BA48" t="inlineStr"/>
+      <c r="AY48" t="n">
+        <v>47</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>0</v>
+      </c>
       <c r="BB48" t="inlineStr"/>
       <c r="BC48" t="inlineStr">
         <is>
@@ -8805,9 +9087,15 @@
         <v>0</v>
       </c>
       <c r="AX49" t="inlineStr"/>
-      <c r="AY49" t="inlineStr"/>
-      <c r="AZ49" t="inlineStr"/>
-      <c r="BA49" t="inlineStr"/>
+      <c r="AY49" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>0</v>
+      </c>
       <c r="BB49" t="inlineStr"/>
       <c r="BC49" t="inlineStr">
         <is>
@@ -8966,9 +9254,15 @@
         <v>0</v>
       </c>
       <c r="AX50" t="inlineStr"/>
-      <c r="AY50" t="inlineStr"/>
-      <c r="AZ50" t="inlineStr"/>
-      <c r="BA50" t="inlineStr"/>
+      <c r="AY50" t="n">
+        <v>49</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>0</v>
+      </c>
       <c r="BB50" t="inlineStr"/>
       <c r="BC50" t="inlineStr">
         <is>
@@ -9127,9 +9421,15 @@
         <v>0</v>
       </c>
       <c r="AX51" t="inlineStr"/>
-      <c r="AY51" t="inlineStr"/>
-      <c r="AZ51" t="inlineStr"/>
-      <c r="BA51" t="inlineStr"/>
+      <c r="AY51" t="n">
+        <v>50</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>0</v>
+      </c>
       <c r="BB51" t="inlineStr"/>
       <c r="BC51" t="inlineStr">
         <is>
@@ -9288,9 +9588,15 @@
         <v>0</v>
       </c>
       <c r="AX52" t="inlineStr"/>
-      <c r="AY52" t="inlineStr"/>
-      <c r="AZ52" t="inlineStr"/>
-      <c r="BA52" t="inlineStr"/>
+      <c r="AY52" t="n">
+        <v>51</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>0</v>
+      </c>
       <c r="BB52" t="inlineStr"/>
       <c r="BC52" t="inlineStr">
         <is>
@@ -9449,9 +9755,15 @@
         <v>0</v>
       </c>
       <c r="AX53" t="inlineStr"/>
-      <c r="AY53" t="inlineStr"/>
-      <c r="AZ53" t="inlineStr"/>
-      <c r="BA53" t="inlineStr"/>
+      <c r="AY53" t="n">
+        <v>52</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>0</v>
+      </c>
       <c r="BB53" t="inlineStr"/>
       <c r="BC53" t="inlineStr">
         <is>
@@ -9610,9 +9922,15 @@
         <v>0</v>
       </c>
       <c r="AX54" t="inlineStr"/>
-      <c r="AY54" t="inlineStr"/>
-      <c r="AZ54" t="inlineStr"/>
-      <c r="BA54" t="inlineStr"/>
+      <c r="AY54" t="n">
+        <v>53</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>0</v>
+      </c>
       <c r="BB54" t="inlineStr"/>
       <c r="BC54" t="inlineStr">
         <is>
@@ -9769,9 +10087,15 @@
         <v>0</v>
       </c>
       <c r="AX55" t="inlineStr"/>
-      <c r="AY55" t="inlineStr"/>
-      <c r="AZ55" t="inlineStr"/>
-      <c r="BA55" t="inlineStr"/>
+      <c r="AY55" t="n">
+        <v>54</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>0</v>
+      </c>
       <c r="BB55" t="inlineStr"/>
       <c r="BC55" t="inlineStr">
         <is>
@@ -9930,9 +10254,15 @@
         <v>0</v>
       </c>
       <c r="AX56" t="inlineStr"/>
-      <c r="AY56" t="inlineStr"/>
-      <c r="AZ56" t="inlineStr"/>
-      <c r="BA56" t="inlineStr"/>
+      <c r="AY56" t="n">
+        <v>55</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>0</v>
+      </c>
       <c r="BB56" t="inlineStr"/>
       <c r="BC56" t="inlineStr">
         <is>
@@ -10091,9 +10421,15 @@
         <v>0</v>
       </c>
       <c r="AX57" t="inlineStr"/>
-      <c r="AY57" t="inlineStr"/>
-      <c r="AZ57" t="inlineStr"/>
-      <c r="BA57" t="inlineStr"/>
+      <c r="AY57" t="n">
+        <v>56</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>0</v>
+      </c>
       <c r="BB57" t="inlineStr"/>
       <c r="BC57" t="inlineStr">
         <is>
@@ -10252,9 +10588,15 @@
         <v>0</v>
       </c>
       <c r="AX58" t="inlineStr"/>
-      <c r="AY58" t="inlineStr"/>
-      <c r="AZ58" t="inlineStr"/>
-      <c r="BA58" t="inlineStr"/>
+      <c r="AY58" t="n">
+        <v>57</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>0</v>
+      </c>
       <c r="BB58" t="inlineStr"/>
       <c r="BC58" t="inlineStr">
         <is>
@@ -10413,9 +10755,15 @@
         <v>0</v>
       </c>
       <c r="AX59" t="inlineStr"/>
-      <c r="AY59" t="inlineStr"/>
-      <c r="AZ59" t="inlineStr"/>
-      <c r="BA59" t="inlineStr"/>
+      <c r="AY59" t="n">
+        <v>58</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>0</v>
+      </c>
       <c r="BB59" t="inlineStr"/>
       <c r="BC59" t="inlineStr">
         <is>
@@ -10574,9 +10922,15 @@
         <v>0</v>
       </c>
       <c r="AX60" t="inlineStr"/>
-      <c r="AY60" t="inlineStr"/>
-      <c r="AZ60" t="inlineStr"/>
-      <c r="BA60" t="inlineStr"/>
+      <c r="AY60" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA60" t="n">
+        <v>0</v>
+      </c>
       <c r="BB60" t="inlineStr"/>
       <c r="BC60" t="inlineStr">
         <is>
@@ -10735,9 +11089,15 @@
         <v>0</v>
       </c>
       <c r="AX61" t="inlineStr"/>
-      <c r="AY61" t="inlineStr"/>
-      <c r="AZ61" t="inlineStr"/>
-      <c r="BA61" t="inlineStr"/>
+      <c r="AY61" t="n">
+        <v>60</v>
+      </c>
+      <c r="AZ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA61" t="n">
+        <v>0</v>
+      </c>
       <c r="BB61" t="inlineStr"/>
       <c r="BC61" t="inlineStr">
         <is>
@@ -10894,9 +11254,15 @@
         <v>0</v>
       </c>
       <c r="AX62" t="inlineStr"/>
-      <c r="AY62" t="inlineStr"/>
-      <c r="AZ62" t="inlineStr"/>
-      <c r="BA62" t="inlineStr"/>
+      <c r="AY62" t="n">
+        <v>61</v>
+      </c>
+      <c r="AZ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA62" t="n">
+        <v>0</v>
+      </c>
       <c r="BB62" t="inlineStr"/>
       <c r="BC62" t="inlineStr">
         <is>
@@ -11053,9 +11419,15 @@
         <v>0</v>
       </c>
       <c r="AX63" t="inlineStr"/>
-      <c r="AY63" t="inlineStr"/>
-      <c r="AZ63" t="inlineStr"/>
-      <c r="BA63" t="inlineStr"/>
+      <c r="AY63" t="n">
+        <v>62</v>
+      </c>
+      <c r="AZ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA63" t="n">
+        <v>0</v>
+      </c>
       <c r="BB63" t="inlineStr"/>
       <c r="BC63" t="inlineStr">
         <is>
@@ -11214,9 +11586,15 @@
         <v>0</v>
       </c>
       <c r="AX64" t="inlineStr"/>
-      <c r="AY64" t="inlineStr"/>
-      <c r="AZ64" t="inlineStr"/>
-      <c r="BA64" t="inlineStr"/>
+      <c r="AY64" t="n">
+        <v>63</v>
+      </c>
+      <c r="AZ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA64" t="n">
+        <v>0</v>
+      </c>
       <c r="BB64" t="inlineStr"/>
       <c r="BC64" t="inlineStr">
         <is>
@@ -11379,9 +11757,15 @@
         <v>0</v>
       </c>
       <c r="AX65" t="inlineStr"/>
-      <c r="AY65" t="inlineStr"/>
-      <c r="AZ65" t="inlineStr"/>
-      <c r="BA65" t="inlineStr"/>
+      <c r="AY65" t="n">
+        <v>64</v>
+      </c>
+      <c r="AZ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA65" t="n">
+        <v>0</v>
+      </c>
       <c r="BB65" t="inlineStr"/>
       <c r="BC65" t="inlineStr">
         <is>
@@ -11536,9 +11920,15 @@
         <v>0</v>
       </c>
       <c r="AX66" t="inlineStr"/>
-      <c r="AY66" t="inlineStr"/>
-      <c r="AZ66" t="inlineStr"/>
-      <c r="BA66" t="inlineStr"/>
+      <c r="AY66" t="n">
+        <v>65</v>
+      </c>
+      <c r="AZ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA66" t="n">
+        <v>0</v>
+      </c>
       <c r="BB66" t="inlineStr"/>
       <c r="BC66" t="inlineStr">
         <is>
@@ -11697,9 +12087,15 @@
         <v>0</v>
       </c>
       <c r="AX67" t="inlineStr"/>
-      <c r="AY67" t="inlineStr"/>
-      <c r="AZ67" t="inlineStr"/>
-      <c r="BA67" t="inlineStr"/>
+      <c r="AY67" t="n">
+        <v>66</v>
+      </c>
+      <c r="AZ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>0</v>
+      </c>
       <c r="BB67" t="inlineStr"/>
       <c r="BC67" t="inlineStr">
         <is>
@@ -11862,9 +12258,15 @@
         <v>0</v>
       </c>
       <c r="AX68" t="inlineStr"/>
-      <c r="AY68" t="inlineStr"/>
-      <c r="AZ68" t="inlineStr"/>
-      <c r="BA68" t="inlineStr"/>
+      <c r="AY68" t="n">
+        <v>67</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>0</v>
+      </c>
       <c r="BB68" t="inlineStr"/>
       <c r="BC68" t="inlineStr">
         <is>
@@ -12021,9 +12423,15 @@
         <v>0</v>
       </c>
       <c r="AX69" t="inlineStr"/>
-      <c r="AY69" t="inlineStr"/>
-      <c r="AZ69" t="inlineStr"/>
-      <c r="BA69" t="inlineStr"/>
+      <c r="AY69" t="n">
+        <v>68</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>0</v>
+      </c>
       <c r="BB69" t="inlineStr"/>
       <c r="BC69" t="inlineStr">
         <is>
@@ -12182,9 +12590,15 @@
         <v>0</v>
       </c>
       <c r="AX70" t="inlineStr"/>
-      <c r="AY70" t="inlineStr"/>
-      <c r="AZ70" t="inlineStr"/>
-      <c r="BA70" t="inlineStr"/>
+      <c r="AY70" t="n">
+        <v>69</v>
+      </c>
+      <c r="AZ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA70" t="n">
+        <v>0</v>
+      </c>
       <c r="BB70" t="inlineStr"/>
       <c r="BC70" t="inlineStr">
         <is>
@@ -12347,9 +12761,15 @@
         <v>0</v>
       </c>
       <c r="AX71" t="inlineStr"/>
-      <c r="AY71" t="inlineStr"/>
-      <c r="AZ71" t="inlineStr"/>
-      <c r="BA71" t="inlineStr"/>
+      <c r="AY71" t="n">
+        <v>70</v>
+      </c>
+      <c r="AZ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA71" t="n">
+        <v>0</v>
+      </c>
       <c r="BB71" t="inlineStr"/>
       <c r="BC71" t="inlineStr">
         <is>
@@ -12508,9 +12928,15 @@
         <v>0</v>
       </c>
       <c r="AX72" t="inlineStr"/>
-      <c r="AY72" t="inlineStr"/>
-      <c r="AZ72" t="inlineStr"/>
-      <c r="BA72" t="inlineStr"/>
+      <c r="AY72" t="n">
+        <v>71</v>
+      </c>
+      <c r="AZ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA72" t="n">
+        <v>0</v>
+      </c>
       <c r="BB72" t="inlineStr"/>
       <c r="BC72" t="inlineStr">
         <is>
@@ -12669,9 +13095,15 @@
         <v>0</v>
       </c>
       <c r="AX73" t="inlineStr"/>
-      <c r="AY73" t="inlineStr"/>
-      <c r="AZ73" t="inlineStr"/>
-      <c r="BA73" t="inlineStr"/>
+      <c r="AY73" t="n">
+        <v>72</v>
+      </c>
+      <c r="AZ73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA73" t="n">
+        <v>0</v>
+      </c>
       <c r="BB73" t="inlineStr"/>
       <c r="BC73" t="inlineStr">
         <is>
@@ -12830,9 +13262,15 @@
         <v>0</v>
       </c>
       <c r="AX74" t="inlineStr"/>
-      <c r="AY74" t="inlineStr"/>
-      <c r="AZ74" t="inlineStr"/>
-      <c r="BA74" t="inlineStr"/>
+      <c r="AY74" t="n">
+        <v>73</v>
+      </c>
+      <c r="AZ74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA74" t="n">
+        <v>0</v>
+      </c>
       <c r="BB74" t="inlineStr"/>
       <c r="BC74" t="inlineStr">
         <is>
@@ -12993,9 +13431,15 @@
         <v>0</v>
       </c>
       <c r="AX75" t="inlineStr"/>
-      <c r="AY75" t="inlineStr"/>
-      <c r="AZ75" t="inlineStr"/>
-      <c r="BA75" t="inlineStr"/>
+      <c r="AY75" t="n">
+        <v>74</v>
+      </c>
+      <c r="AZ75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA75" t="n">
+        <v>0</v>
+      </c>
       <c r="BB75" t="inlineStr"/>
       <c r="BC75" t="inlineStr">
         <is>
@@ -13047,7 +13491,7 @@
         <v>5.2</v>
       </c>
       <c r="K76" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="L76" t="n">
         <v>33.4</v>
@@ -13154,9 +13598,15 @@
         <v>0</v>
       </c>
       <c r="AX76" t="inlineStr"/>
-      <c r="AY76" t="inlineStr"/>
-      <c r="AZ76" t="inlineStr"/>
-      <c r="BA76" t="inlineStr"/>
+      <c r="AY76" t="n">
+        <v>75</v>
+      </c>
+      <c r="AZ76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA76" t="n">
+        <v>0</v>
+      </c>
       <c r="BB76" t="inlineStr"/>
       <c r="BC76" t="inlineStr">
         <is>
@@ -13315,9 +13765,15 @@
         <v>0</v>
       </c>
       <c r="AX77" t="inlineStr"/>
-      <c r="AY77" t="inlineStr"/>
-      <c r="AZ77" t="inlineStr"/>
-      <c r="BA77" t="inlineStr"/>
+      <c r="AY77" t="n">
+        <v>76</v>
+      </c>
+      <c r="AZ77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA77" t="n">
+        <v>0</v>
+      </c>
       <c r="BB77" t="inlineStr"/>
       <c r="BC77" t="inlineStr">
         <is>
@@ -13476,9 +13932,15 @@
         <v>0</v>
       </c>
       <c r="AX78" t="inlineStr"/>
-      <c r="AY78" t="inlineStr"/>
-      <c r="AZ78" t="inlineStr"/>
-      <c r="BA78" t="inlineStr"/>
+      <c r="AY78" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>0</v>
+      </c>
       <c r="BB78" t="inlineStr"/>
       <c r="BC78" t="inlineStr">
         <is>
@@ -13637,9 +14099,15 @@
         <v>0</v>
       </c>
       <c r="AX79" t="inlineStr"/>
-      <c r="AY79" t="inlineStr"/>
-      <c r="AZ79" t="inlineStr"/>
-      <c r="BA79" t="inlineStr"/>
+      <c r="AY79" t="n">
+        <v>78</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>0</v>
+      </c>
       <c r="BB79" t="inlineStr"/>
       <c r="BC79" t="inlineStr">
         <is>
@@ -13802,9 +14270,15 @@
         <v>0</v>
       </c>
       <c r="AX80" t="inlineStr"/>
-      <c r="AY80" t="inlineStr"/>
-      <c r="AZ80" t="inlineStr"/>
-      <c r="BA80" t="inlineStr"/>
+      <c r="AY80" t="n">
+        <v>79</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>0</v>
+      </c>
       <c r="BB80" t="inlineStr"/>
       <c r="BC80" t="inlineStr">
         <is>
@@ -13961,9 +14435,15 @@
         <v>0</v>
       </c>
       <c r="AX81" t="inlineStr"/>
-      <c r="AY81" t="inlineStr"/>
-      <c r="AZ81" t="inlineStr"/>
-      <c r="BA81" t="inlineStr"/>
+      <c r="AY81" t="n">
+        <v>80</v>
+      </c>
+      <c r="AZ81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA81" t="n">
+        <v>0</v>
+      </c>
       <c r="BB81" t="inlineStr"/>
       <c r="BC81" t="inlineStr">
         <is>
@@ -14126,9 +14606,15 @@
         <v>0</v>
       </c>
       <c r="AX82" t="inlineStr"/>
-      <c r="AY82" t="inlineStr"/>
-      <c r="AZ82" t="inlineStr"/>
-      <c r="BA82" t="inlineStr"/>
+      <c r="AY82" t="n">
+        <v>81</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>0</v>
+      </c>
       <c r="BB82" t="inlineStr"/>
       <c r="BC82" t="inlineStr">
         <is>
@@ -14287,9 +14773,15 @@
         <v>0</v>
       </c>
       <c r="AX83" t="inlineStr"/>
-      <c r="AY83" t="inlineStr"/>
-      <c r="AZ83" t="inlineStr"/>
-      <c r="BA83" t="inlineStr"/>
+      <c r="AY83" t="n">
+        <v>82</v>
+      </c>
+      <c r="AZ83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA83" t="n">
+        <v>0</v>
+      </c>
       <c r="BB83" t="inlineStr"/>
       <c r="BC83" t="inlineStr">
         <is>
@@ -14448,9 +14940,15 @@
         <v>0</v>
       </c>
       <c r="AX84" t="inlineStr"/>
-      <c r="AY84" t="inlineStr"/>
-      <c r="AZ84" t="inlineStr"/>
-      <c r="BA84" t="inlineStr"/>
+      <c r="AY84" t="n">
+        <v>83</v>
+      </c>
+      <c r="AZ84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA84" t="n">
+        <v>0</v>
+      </c>
       <c r="BB84" t="inlineStr"/>
       <c r="BC84" t="inlineStr">
         <is>
@@ -14609,9 +15107,15 @@
         <v>0</v>
       </c>
       <c r="AX85" t="inlineStr"/>
-      <c r="AY85" t="inlineStr"/>
-      <c r="AZ85" t="inlineStr"/>
-      <c r="BA85" t="inlineStr"/>
+      <c r="AY85" t="n">
+        <v>84</v>
+      </c>
+      <c r="AZ85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA85" t="n">
+        <v>0</v>
+      </c>
       <c r="BB85" t="inlineStr"/>
       <c r="BC85" t="inlineStr">
         <is>
@@ -14770,9 +15274,15 @@
         <v>0</v>
       </c>
       <c r="AX86" t="inlineStr"/>
-      <c r="AY86" t="inlineStr"/>
-      <c r="AZ86" t="inlineStr"/>
-      <c r="BA86" t="inlineStr"/>
+      <c r="AY86" t="n">
+        <v>85</v>
+      </c>
+      <c r="AZ86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA86" t="n">
+        <v>0</v>
+      </c>
       <c r="BB86" t="inlineStr"/>
       <c r="BC86" t="inlineStr">
         <is>
@@ -14931,9 +15441,15 @@
         <v>0</v>
       </c>
       <c r="AX87" t="inlineStr"/>
-      <c r="AY87" t="inlineStr"/>
-      <c r="AZ87" t="inlineStr"/>
-      <c r="BA87" t="inlineStr"/>
+      <c r="AY87" t="n">
+        <v>86</v>
+      </c>
+      <c r="AZ87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA87" t="n">
+        <v>0</v>
+      </c>
       <c r="BB87" t="inlineStr"/>
       <c r="BC87" t="inlineStr">
         <is>
@@ -15092,9 +15608,15 @@
         <v>0</v>
       </c>
       <c r="AX88" t="inlineStr"/>
-      <c r="AY88" t="inlineStr"/>
-      <c r="AZ88" t="inlineStr"/>
-      <c r="BA88" t="inlineStr"/>
+      <c r="AY88" t="n">
+        <v>87</v>
+      </c>
+      <c r="AZ88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA88" t="n">
+        <v>0</v>
+      </c>
       <c r="BB88" t="inlineStr"/>
       <c r="BC88" t="inlineStr">
         <is>
@@ -15253,9 +15775,15 @@
         <v>0</v>
       </c>
       <c r="AX89" t="inlineStr"/>
-      <c r="AY89" t="inlineStr"/>
-      <c r="AZ89" t="inlineStr"/>
-      <c r="BA89" t="inlineStr"/>
+      <c r="AY89" t="n">
+        <v>88</v>
+      </c>
+      <c r="AZ89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA89" t="n">
+        <v>0</v>
+      </c>
       <c r="BB89" t="inlineStr"/>
       <c r="BC89" t="inlineStr">
         <is>
@@ -15414,9 +15942,15 @@
         <v>0</v>
       </c>
       <c r="AX90" t="inlineStr"/>
-      <c r="AY90" t="inlineStr"/>
-      <c r="AZ90" t="inlineStr"/>
-      <c r="BA90" t="inlineStr"/>
+      <c r="AY90" t="n">
+        <v>89</v>
+      </c>
+      <c r="AZ90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA90" t="n">
+        <v>0</v>
+      </c>
       <c r="BB90" t="inlineStr"/>
       <c r="BC90" t="inlineStr">
         <is>
@@ -15575,9 +16109,15 @@
         <v>0</v>
       </c>
       <c r="AX91" t="inlineStr"/>
-      <c r="AY91" t="inlineStr"/>
-      <c r="AZ91" t="inlineStr"/>
-      <c r="BA91" t="inlineStr"/>
+      <c r="AY91" t="n">
+        <v>90</v>
+      </c>
+      <c r="AZ91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA91" t="n">
+        <v>0</v>
+      </c>
       <c r="BB91" t="inlineStr"/>
       <c r="BC91" t="inlineStr">
         <is>
@@ -15734,9 +16274,15 @@
         <v>0</v>
       </c>
       <c r="AX92" t="inlineStr"/>
-      <c r="AY92" t="inlineStr"/>
-      <c r="AZ92" t="inlineStr"/>
-      <c r="BA92" t="inlineStr"/>
+      <c r="AY92" t="n">
+        <v>91</v>
+      </c>
+      <c r="AZ92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA92" t="n">
+        <v>0</v>
+      </c>
       <c r="BB92" t="inlineStr"/>
       <c r="BC92" t="inlineStr">
         <is>
@@ -15899,9 +16445,15 @@
         <v>0</v>
       </c>
       <c r="AX93" t="inlineStr"/>
-      <c r="AY93" t="inlineStr"/>
-      <c r="AZ93" t="inlineStr"/>
-      <c r="BA93" t="inlineStr"/>
+      <c r="AY93" t="n">
+        <v>92</v>
+      </c>
+      <c r="AZ93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA93" t="n">
+        <v>0</v>
+      </c>
       <c r="BB93" t="inlineStr"/>
       <c r="BC93" t="inlineStr">
         <is>
@@ -16060,9 +16612,15 @@
         <v>0</v>
       </c>
       <c r="AX94" t="inlineStr"/>
-      <c r="AY94" t="inlineStr"/>
-      <c r="AZ94" t="inlineStr"/>
-      <c r="BA94" t="inlineStr"/>
+      <c r="AY94" t="n">
+        <v>93</v>
+      </c>
+      <c r="AZ94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA94" t="n">
+        <v>0</v>
+      </c>
       <c r="BB94" t="inlineStr"/>
       <c r="BC94" t="inlineStr">
         <is>
@@ -16219,9 +16777,15 @@
         <v>0</v>
       </c>
       <c r="AX95" t="inlineStr"/>
-      <c r="AY95" t="inlineStr"/>
-      <c r="AZ95" t="inlineStr"/>
-      <c r="BA95" t="inlineStr"/>
+      <c r="AY95" t="n">
+        <v>94</v>
+      </c>
+      <c r="AZ95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA95" t="n">
+        <v>0</v>
+      </c>
       <c r="BB95" t="inlineStr"/>
       <c r="BC95" t="inlineStr">
         <is>
@@ -16378,9 +16942,15 @@
         <v>0</v>
       </c>
       <c r="AX96" t="inlineStr"/>
-      <c r="AY96" t="inlineStr"/>
-      <c r="AZ96" t="inlineStr"/>
-      <c r="BA96" t="inlineStr"/>
+      <c r="AY96" t="n">
+        <v>95</v>
+      </c>
+      <c r="AZ96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA96" t="n">
+        <v>0</v>
+      </c>
       <c r="BB96" t="inlineStr"/>
       <c r="BC96" t="inlineStr">
         <is>
@@ -16543,9 +17113,15 @@
         <v>0</v>
       </c>
       <c r="AX97" t="inlineStr"/>
-      <c r="AY97" t="inlineStr"/>
-      <c r="AZ97" t="inlineStr"/>
-      <c r="BA97" t="inlineStr"/>
+      <c r="AY97" t="n">
+        <v>96</v>
+      </c>
+      <c r="AZ97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA97" t="n">
+        <v>0</v>
+      </c>
       <c r="BB97" t="inlineStr"/>
       <c r="BC97" t="inlineStr">
         <is>
@@ -16702,9 +17278,15 @@
         <v>0</v>
       </c>
       <c r="AX98" t="inlineStr"/>
-      <c r="AY98" t="inlineStr"/>
-      <c r="AZ98" t="inlineStr"/>
-      <c r="BA98" t="inlineStr"/>
+      <c r="AY98" t="n">
+        <v>97</v>
+      </c>
+      <c r="AZ98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA98" t="n">
+        <v>0</v>
+      </c>
       <c r="BB98" t="inlineStr"/>
       <c r="BC98" t="inlineStr">
         <is>
@@ -16861,9 +17443,15 @@
         <v>0</v>
       </c>
       <c r="AX99" t="inlineStr"/>
-      <c r="AY99" t="inlineStr"/>
-      <c r="AZ99" t="inlineStr"/>
-      <c r="BA99" t="inlineStr"/>
+      <c r="AY99" t="n">
+        <v>98</v>
+      </c>
+      <c r="AZ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA99" t="n">
+        <v>0</v>
+      </c>
       <c r="BB99" t="inlineStr"/>
       <c r="BC99" t="inlineStr">
         <is>
@@ -17022,9 +17610,15 @@
         <v>0</v>
       </c>
       <c r="AX100" t="inlineStr"/>
-      <c r="AY100" t="inlineStr"/>
-      <c r="AZ100" t="inlineStr"/>
-      <c r="BA100" t="inlineStr"/>
+      <c r="AY100" t="n">
+        <v>99</v>
+      </c>
+      <c r="AZ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA100" t="n">
+        <v>0</v>
+      </c>
       <c r="BB100" t="inlineStr"/>
       <c r="BC100" t="inlineStr">
         <is>
@@ -17183,9 +17777,15 @@
         <v>0</v>
       </c>
       <c r="AX101" t="inlineStr"/>
-      <c r="AY101" t="inlineStr"/>
-      <c r="AZ101" t="inlineStr"/>
-      <c r="BA101" t="inlineStr"/>
+      <c r="AY101" t="n">
+        <v>100</v>
+      </c>
+      <c r="AZ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA101" t="n">
+        <v>0</v>
+      </c>
       <c r="BB101" t="inlineStr"/>
       <c r="BC101" t="inlineStr">
         <is>
@@ -17344,9 +17944,15 @@
         <v>0</v>
       </c>
       <c r="AX102" t="inlineStr"/>
-      <c r="AY102" t="inlineStr"/>
-      <c r="AZ102" t="inlineStr"/>
-      <c r="BA102" t="inlineStr"/>
+      <c r="AY102" t="n">
+        <v>101</v>
+      </c>
+      <c r="AZ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA102" t="n">
+        <v>0</v>
+      </c>
       <c r="BB102" t="inlineStr"/>
       <c r="BC102" t="inlineStr">
         <is>
@@ -17505,9 +18111,15 @@
         <v>0</v>
       </c>
       <c r="AX103" t="inlineStr"/>
-      <c r="AY103" t="inlineStr"/>
-      <c r="AZ103" t="inlineStr"/>
-      <c r="BA103" t="inlineStr"/>
+      <c r="AY103" t="n">
+        <v>102</v>
+      </c>
+      <c r="AZ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA103" t="n">
+        <v>0</v>
+      </c>
       <c r="BB103" t="inlineStr"/>
       <c r="BC103" t="inlineStr">
         <is>
@@ -17666,9 +18278,15 @@
         <v>0</v>
       </c>
       <c r="AX104" t="inlineStr"/>
-      <c r="AY104" t="inlineStr"/>
-      <c r="AZ104" t="inlineStr"/>
-      <c r="BA104" t="inlineStr"/>
+      <c r="AY104" t="n">
+        <v>103</v>
+      </c>
+      <c r="AZ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA104" t="n">
+        <v>0</v>
+      </c>
       <c r="BB104" t="inlineStr"/>
       <c r="BC104" t="inlineStr">
         <is>
@@ -17823,9 +18441,15 @@
         <v>0</v>
       </c>
       <c r="AX105" t="inlineStr"/>
-      <c r="AY105" t="inlineStr"/>
-      <c r="AZ105" t="inlineStr"/>
-      <c r="BA105" t="inlineStr"/>
+      <c r="AY105" t="n">
+        <v>104</v>
+      </c>
+      <c r="AZ105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA105" t="n">
+        <v>0</v>
+      </c>
       <c r="BB105" t="inlineStr"/>
       <c r="BC105" t="inlineStr">
         <is>
@@ -17984,9 +18608,15 @@
         <v>0</v>
       </c>
       <c r="AX106" t="inlineStr"/>
-      <c r="AY106" t="inlineStr"/>
-      <c r="AZ106" t="inlineStr"/>
-      <c r="BA106" t="inlineStr"/>
+      <c r="AY106" t="n">
+        <v>105</v>
+      </c>
+      <c r="AZ106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA106" t="n">
+        <v>0</v>
+      </c>
       <c r="BB106" t="inlineStr"/>
       <c r="BC106" t="inlineStr">
         <is>
@@ -18143,9 +18773,15 @@
         <v>0</v>
       </c>
       <c r="AX107" t="inlineStr"/>
-      <c r="AY107" t="inlineStr"/>
-      <c r="AZ107" t="inlineStr"/>
-      <c r="BA107" t="inlineStr"/>
+      <c r="AY107" t="n">
+        <v>106</v>
+      </c>
+      <c r="AZ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA107" t="n">
+        <v>0</v>
+      </c>
       <c r="BB107" t="inlineStr"/>
       <c r="BC107" t="inlineStr">
         <is>
@@ -18304,9 +18940,15 @@
         <v>0</v>
       </c>
       <c r="AX108" t="inlineStr"/>
-      <c r="AY108" t="inlineStr"/>
-      <c r="AZ108" t="inlineStr"/>
-      <c r="BA108" t="inlineStr"/>
+      <c r="AY108" t="n">
+        <v>107</v>
+      </c>
+      <c r="AZ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA108" t="n">
+        <v>0</v>
+      </c>
       <c r="BB108" t="inlineStr"/>
       <c r="BC108" t="inlineStr">
         <is>
@@ -18461,9 +19103,15 @@
         <v>0</v>
       </c>
       <c r="AX109" t="inlineStr"/>
-      <c r="AY109" t="inlineStr"/>
-      <c r="AZ109" t="inlineStr"/>
-      <c r="BA109" t="inlineStr"/>
+      <c r="AY109" t="n">
+        <v>108</v>
+      </c>
+      <c r="AZ109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA109" t="n">
+        <v>0</v>
+      </c>
       <c r="BB109" t="inlineStr"/>
       <c r="BC109" t="inlineStr">
         <is>
@@ -18622,9 +19270,15 @@
         <v>0</v>
       </c>
       <c r="AX110" t="inlineStr"/>
-      <c r="AY110" t="inlineStr"/>
-      <c r="AZ110" t="inlineStr"/>
-      <c r="BA110" t="inlineStr"/>
+      <c r="AY110" t="n">
+        <v>109</v>
+      </c>
+      <c r="AZ110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA110" t="n">
+        <v>0</v>
+      </c>
       <c r="BB110" t="inlineStr"/>
       <c r="BC110" t="inlineStr">
         <is>
@@ -18783,9 +19437,15 @@
         <v>0</v>
       </c>
       <c r="AX111" t="inlineStr"/>
-      <c r="AY111" t="inlineStr"/>
-      <c r="AZ111" t="inlineStr"/>
-      <c r="BA111" t="inlineStr"/>
+      <c r="AY111" t="n">
+        <v>110</v>
+      </c>
+      <c r="AZ111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA111" t="n">
+        <v>0</v>
+      </c>
       <c r="BB111" t="inlineStr"/>
       <c r="BC111" t="inlineStr">
         <is>
@@ -18942,9 +19602,15 @@
         <v>0</v>
       </c>
       <c r="AX112" t="inlineStr"/>
-      <c r="AY112" t="inlineStr"/>
-      <c r="AZ112" t="inlineStr"/>
-      <c r="BA112" t="inlineStr"/>
+      <c r="AY112" t="n">
+        <v>111</v>
+      </c>
+      <c r="AZ112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA112" t="n">
+        <v>0</v>
+      </c>
       <c r="BB112" t="inlineStr"/>
       <c r="BC112" t="inlineStr">
         <is>
@@ -19103,9 +19769,15 @@
         <v>0</v>
       </c>
       <c r="AX113" t="inlineStr"/>
-      <c r="AY113" t="inlineStr"/>
-      <c r="AZ113" t="inlineStr"/>
-      <c r="BA113" t="inlineStr"/>
+      <c r="AY113" t="n">
+        <v>112</v>
+      </c>
+      <c r="AZ113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA113" t="n">
+        <v>0</v>
+      </c>
       <c r="BB113" t="inlineStr"/>
       <c r="BC113" t="inlineStr">
         <is>
@@ -19264,9 +19936,15 @@
         <v>0</v>
       </c>
       <c r="AX114" t="inlineStr"/>
-      <c r="AY114" t="inlineStr"/>
-      <c r="AZ114" t="inlineStr"/>
-      <c r="BA114" t="inlineStr"/>
+      <c r="AY114" t="n">
+        <v>113</v>
+      </c>
+      <c r="AZ114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA114" t="n">
+        <v>0</v>
+      </c>
       <c r="BB114" t="inlineStr"/>
       <c r="BC114" t="inlineStr">
         <is>
@@ -19425,9 +20103,15 @@
         <v>0</v>
       </c>
       <c r="AX115" t="inlineStr"/>
-      <c r="AY115" t="inlineStr"/>
-      <c r="AZ115" t="inlineStr"/>
-      <c r="BA115" t="inlineStr"/>
+      <c r="AY115" t="n">
+        <v>114</v>
+      </c>
+      <c r="AZ115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA115" t="n">
+        <v>0</v>
+      </c>
       <c r="BB115" t="inlineStr"/>
       <c r="BC115" t="inlineStr">
         <is>
@@ -19586,9 +20270,15 @@
         <v>0</v>
       </c>
       <c r="AX116" t="inlineStr"/>
-      <c r="AY116" t="inlineStr"/>
-      <c r="AZ116" t="inlineStr"/>
-      <c r="BA116" t="inlineStr"/>
+      <c r="AY116" t="n">
+        <v>115</v>
+      </c>
+      <c r="AZ116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA116" t="n">
+        <v>0</v>
+      </c>
       <c r="BB116" t="inlineStr"/>
       <c r="BC116" t="inlineStr">
         <is>
@@ -19747,9 +20437,15 @@
         <v>0</v>
       </c>
       <c r="AX117" t="inlineStr"/>
-      <c r="AY117" t="inlineStr"/>
-      <c r="AZ117" t="inlineStr"/>
-      <c r="BA117" t="inlineStr"/>
+      <c r="AY117" t="n">
+        <v>116</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0</v>
+      </c>
       <c r="BB117" t="inlineStr"/>
       <c r="BC117" t="inlineStr">
         <is>
@@ -19908,9 +20604,15 @@
         <v>0</v>
       </c>
       <c r="AX118" t="inlineStr"/>
-      <c r="AY118" t="inlineStr"/>
-      <c r="AZ118" t="inlineStr"/>
-      <c r="BA118" t="inlineStr"/>
+      <c r="AY118" t="n">
+        <v>117</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0</v>
+      </c>
       <c r="BB118" t="inlineStr"/>
       <c r="BC118" t="inlineStr">
         <is>
@@ -20073,9 +20775,15 @@
         <v>0</v>
       </c>
       <c r="AX119" t="inlineStr"/>
-      <c r="AY119" t="inlineStr"/>
-      <c r="AZ119" t="inlineStr"/>
-      <c r="BA119" t="inlineStr"/>
+      <c r="AY119" t="n">
+        <v>118</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0</v>
+      </c>
       <c r="BB119" t="inlineStr"/>
       <c r="BC119" t="inlineStr">
         <is>
@@ -20234,9 +20942,15 @@
         <v>0</v>
       </c>
       <c r="AX120" t="inlineStr"/>
-      <c r="AY120" t="inlineStr"/>
-      <c r="AZ120" t="inlineStr"/>
-      <c r="BA120" t="inlineStr"/>
+      <c r="AY120" t="n">
+        <v>119</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0</v>
+      </c>
       <c r="BB120" t="inlineStr"/>
       <c r="BC120" t="inlineStr">
         <is>
@@ -20393,9 +21107,15 @@
         <v>0</v>
       </c>
       <c r="AX121" t="inlineStr"/>
-      <c r="AY121" t="inlineStr"/>
-      <c r="AZ121" t="inlineStr"/>
-      <c r="BA121" t="inlineStr"/>
+      <c r="AY121" t="n">
+        <v>120</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0</v>
+      </c>
       <c r="BB121" t="inlineStr"/>
       <c r="BC121" t="inlineStr">
         <is>
@@ -20554,9 +21274,15 @@
         <v>0</v>
       </c>
       <c r="AX122" t="inlineStr"/>
-      <c r="AY122" t="inlineStr"/>
-      <c r="AZ122" t="inlineStr"/>
-      <c r="BA122" t="inlineStr"/>
+      <c r="AY122" t="n">
+        <v>121</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0</v>
+      </c>
       <c r="BB122" t="inlineStr"/>
       <c r="BC122" t="inlineStr">
         <is>
@@ -20719,9 +21445,15 @@
         <v>0</v>
       </c>
       <c r="AX123" t="inlineStr"/>
-      <c r="AY123" t="inlineStr"/>
-      <c r="AZ123" t="inlineStr"/>
-      <c r="BA123" t="inlineStr"/>
+      <c r="AY123" t="n">
+        <v>122</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0</v>
+      </c>
       <c r="BB123" t="inlineStr"/>
       <c r="BC123" t="inlineStr">
         <is>
@@ -20880,9 +21612,15 @@
         <v>0</v>
       </c>
       <c r="AX124" t="inlineStr"/>
-      <c r="AY124" t="inlineStr"/>
-      <c r="AZ124" t="inlineStr"/>
-      <c r="BA124" t="inlineStr"/>
+      <c r="AY124" t="n">
+        <v>123</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0</v>
+      </c>
       <c r="BB124" t="inlineStr"/>
       <c r="BC124" t="inlineStr">
         <is>
@@ -21041,9 +21779,15 @@
         <v>0</v>
       </c>
       <c r="AX125" t="inlineStr"/>
-      <c r="AY125" t="inlineStr"/>
-      <c r="AZ125" t="inlineStr"/>
-      <c r="BA125" t="inlineStr"/>
+      <c r="AY125" t="n">
+        <v>124</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0</v>
+      </c>
       <c r="BB125" t="inlineStr"/>
       <c r="BC125" t="inlineStr">
         <is>
@@ -21202,9 +21946,15 @@
         <v>0</v>
       </c>
       <c r="AX126" t="inlineStr"/>
-      <c r="AY126" t="inlineStr"/>
-      <c r="AZ126" t="inlineStr"/>
-      <c r="BA126" t="inlineStr"/>
+      <c r="AY126" t="n">
+        <v>125</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0</v>
+      </c>
       <c r="BB126" t="inlineStr"/>
       <c r="BC126" t="inlineStr">
         <is>
@@ -21365,9 +22115,15 @@
         <v>0</v>
       </c>
       <c r="AX127" t="inlineStr"/>
-      <c r="AY127" t="inlineStr"/>
-      <c r="AZ127" t="inlineStr"/>
-      <c r="BA127" t="inlineStr"/>
+      <c r="AY127" t="n">
+        <v>126</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0</v>
+      </c>
       <c r="BB127" t="inlineStr"/>
       <c r="BC127" t="inlineStr">
         <is>
@@ -21526,9 +22282,15 @@
         <v>0</v>
       </c>
       <c r="AX128" t="inlineStr"/>
-      <c r="AY128" t="inlineStr"/>
-      <c r="AZ128" t="inlineStr"/>
-      <c r="BA128" t="inlineStr"/>
+      <c r="AY128" t="n">
+        <v>127</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0</v>
+      </c>
       <c r="BB128" t="inlineStr"/>
       <c r="BC128" t="inlineStr">
         <is>
@@ -21687,9 +22449,15 @@
         <v>0</v>
       </c>
       <c r="AX129" t="inlineStr"/>
-      <c r="AY129" t="inlineStr"/>
-      <c r="AZ129" t="inlineStr"/>
-      <c r="BA129" t="inlineStr"/>
+      <c r="AY129" t="n">
+        <v>128</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0</v>
+      </c>
       <c r="BB129" t="inlineStr"/>
       <c r="BC129" t="inlineStr">
         <is>
@@ -21848,9 +22616,15 @@
         <v>0</v>
       </c>
       <c r="AX130" t="inlineStr"/>
-      <c r="AY130" t="inlineStr"/>
-      <c r="AZ130" t="inlineStr"/>
-      <c r="BA130" t="inlineStr"/>
+      <c r="AY130" t="n">
+        <v>129</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0</v>
+      </c>
       <c r="BB130" t="inlineStr"/>
       <c r="BC130" t="inlineStr">
         <is>
@@ -22011,9 +22785,15 @@
         <v>0</v>
       </c>
       <c r="AX131" t="inlineStr"/>
-      <c r="AY131" t="inlineStr"/>
-      <c r="AZ131" t="inlineStr"/>
-      <c r="BA131" t="inlineStr"/>
+      <c r="AY131" t="n">
+        <v>130</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0</v>
+      </c>
       <c r="BB131" t="inlineStr"/>
       <c r="BC131" t="inlineStr">
         <is>
@@ -22166,9 +22946,15 @@
         <v>0</v>
       </c>
       <c r="AX132" t="inlineStr"/>
-      <c r="AY132" t="inlineStr"/>
-      <c r="AZ132" t="inlineStr"/>
-      <c r="BA132" t="inlineStr"/>
+      <c r="AY132" t="n">
+        <v>131</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0</v>
+      </c>
       <c r="BB132" t="inlineStr"/>
       <c r="BC132" t="inlineStr">
         <is>
@@ -22325,9 +23111,15 @@
         <v>0</v>
       </c>
       <c r="AX133" t="inlineStr"/>
-      <c r="AY133" t="inlineStr"/>
-      <c r="AZ133" t="inlineStr"/>
-      <c r="BA133" t="inlineStr"/>
+      <c r="AY133" t="n">
+        <v>132</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0</v>
+      </c>
       <c r="BB133" t="inlineStr"/>
       <c r="BC133" t="inlineStr">
         <is>
@@ -22484,9 +23276,15 @@
         <v>0</v>
       </c>
       <c r="AX134" t="inlineStr"/>
-      <c r="AY134" t="inlineStr"/>
-      <c r="AZ134" t="inlineStr"/>
-      <c r="BA134" t="inlineStr"/>
+      <c r="AY134" t="n">
+        <v>133</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0</v>
+      </c>
       <c r="BB134" t="inlineStr"/>
       <c r="BC134" t="inlineStr">
         <is>
@@ -22645,9 +23443,15 @@
         <v>0</v>
       </c>
       <c r="AX135" t="inlineStr"/>
-      <c r="AY135" t="inlineStr"/>
-      <c r="AZ135" t="inlineStr"/>
-      <c r="BA135" t="inlineStr"/>
+      <c r="AY135" t="n">
+        <v>134</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0</v>
+      </c>
       <c r="BB135" t="inlineStr"/>
       <c r="BC135" t="inlineStr">
         <is>
@@ -22806,9 +23610,15 @@
         <v>0</v>
       </c>
       <c r="AX136" t="inlineStr"/>
-      <c r="AY136" t="inlineStr"/>
-      <c r="AZ136" t="inlineStr"/>
-      <c r="BA136" t="inlineStr"/>
+      <c r="AY136" t="n">
+        <v>135</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0</v>
+      </c>
       <c r="BB136" t="inlineStr"/>
       <c r="BC136" t="inlineStr">
         <is>
@@ -22965,9 +23775,15 @@
         <v>0</v>
       </c>
       <c r="AX137" t="inlineStr"/>
-      <c r="AY137" t="inlineStr"/>
-      <c r="AZ137" t="inlineStr"/>
-      <c r="BA137" t="inlineStr"/>
+      <c r="AY137" t="n">
+        <v>136</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0</v>
+      </c>
       <c r="BB137" t="inlineStr"/>
       <c r="BC137" t="inlineStr">
         <is>
@@ -23126,9 +23942,15 @@
         <v>0</v>
       </c>
       <c r="AX138" t="inlineStr"/>
-      <c r="AY138" t="inlineStr"/>
-      <c r="AZ138" t="inlineStr"/>
-      <c r="BA138" t="inlineStr"/>
+      <c r="AY138" t="n">
+        <v>137</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0</v>
+      </c>
       <c r="BB138" t="inlineStr"/>
       <c r="BC138" t="inlineStr">
         <is>
@@ -23287,9 +24109,15 @@
         <v>0</v>
       </c>
       <c r="AX139" t="inlineStr"/>
-      <c r="AY139" t="inlineStr"/>
-      <c r="AZ139" t="inlineStr"/>
-      <c r="BA139" t="inlineStr"/>
+      <c r="AY139" t="n">
+        <v>138</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0</v>
+      </c>
       <c r="BB139" t="inlineStr"/>
       <c r="BC139" t="inlineStr">
         <is>
@@ -23448,9 +24276,15 @@
         <v>0</v>
       </c>
       <c r="AX140" t="inlineStr"/>
-      <c r="AY140" t="inlineStr"/>
-      <c r="AZ140" t="inlineStr"/>
-      <c r="BA140" t="inlineStr"/>
+      <c r="AY140" t="n">
+        <v>139</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0</v>
+      </c>
       <c r="BB140" t="inlineStr"/>
       <c r="BC140" t="inlineStr">
         <is>
@@ -23613,9 +24447,15 @@
         <v>0</v>
       </c>
       <c r="AX141" t="inlineStr"/>
-      <c r="AY141" t="inlineStr"/>
-      <c r="AZ141" t="inlineStr"/>
-      <c r="BA141" t="inlineStr"/>
+      <c r="AY141" t="n">
+        <v>140</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0</v>
+      </c>
       <c r="BB141" t="inlineStr"/>
       <c r="BC141" t="inlineStr">
         <is>
@@ -23778,9 +24618,15 @@
         <v>0</v>
       </c>
       <c r="AX142" t="inlineStr"/>
-      <c r="AY142" t="inlineStr"/>
-      <c r="AZ142" t="inlineStr"/>
-      <c r="BA142" t="inlineStr"/>
+      <c r="AY142" t="n">
+        <v>141</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0</v>
+      </c>
       <c r="BB142" t="inlineStr"/>
       <c r="BC142" t="inlineStr">
         <is>
@@ -23939,9 +24785,15 @@
         <v>0</v>
       </c>
       <c r="AX143" t="inlineStr"/>
-      <c r="AY143" t="inlineStr"/>
-      <c r="AZ143" t="inlineStr"/>
-      <c r="BA143" t="inlineStr"/>
+      <c r="AY143" t="n">
+        <v>142</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0</v>
+      </c>
       <c r="BB143" t="inlineStr"/>
       <c r="BC143" t="inlineStr">
         <is>
@@ -24100,9 +24952,15 @@
         <v>0</v>
       </c>
       <c r="AX144" t="inlineStr"/>
-      <c r="AY144" t="inlineStr"/>
-      <c r="AZ144" t="inlineStr"/>
-      <c r="BA144" t="inlineStr"/>
+      <c r="AY144" t="n">
+        <v>143</v>
+      </c>
+      <c r="AZ144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA144" t="n">
+        <v>0</v>
+      </c>
       <c r="BB144" t="inlineStr"/>
       <c r="BC144" t="inlineStr">
         <is>
@@ -24261,9 +25119,15 @@
         <v>0</v>
       </c>
       <c r="AX145" t="inlineStr"/>
-      <c r="AY145" t="inlineStr"/>
-      <c r="AZ145" t="inlineStr"/>
-      <c r="BA145" t="inlineStr"/>
+      <c r="AY145" t="n">
+        <v>144</v>
+      </c>
+      <c r="AZ145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA145" t="n">
+        <v>0</v>
+      </c>
       <c r="BB145" t="inlineStr"/>
       <c r="BC145" t="inlineStr">
         <is>
@@ -24422,9 +25286,15 @@
         <v>0</v>
       </c>
       <c r="AX146" t="inlineStr"/>
-      <c r="AY146" t="inlineStr"/>
-      <c r="AZ146" t="inlineStr"/>
-      <c r="BA146" t="inlineStr"/>
+      <c r="AY146" t="n">
+        <v>145</v>
+      </c>
+      <c r="AZ146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA146" t="n">
+        <v>0</v>
+      </c>
       <c r="BB146" t="inlineStr"/>
       <c r="BC146" t="inlineStr">
         <is>
@@ -24583,9 +25453,15 @@
         <v>0</v>
       </c>
       <c r="AX147" t="inlineStr"/>
-      <c r="AY147" t="inlineStr"/>
-      <c r="AZ147" t="inlineStr"/>
-      <c r="BA147" t="inlineStr"/>
+      <c r="AY147" t="n">
+        <v>146</v>
+      </c>
+      <c r="AZ147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA147" t="n">
+        <v>0</v>
+      </c>
       <c r="BB147" t="inlineStr"/>
       <c r="BC147" t="inlineStr">
         <is>
@@ -24744,9 +25620,15 @@
         <v>0</v>
       </c>
       <c r="AX148" t="inlineStr"/>
-      <c r="AY148" t="inlineStr"/>
-      <c r="AZ148" t="inlineStr"/>
-      <c r="BA148" t="inlineStr"/>
+      <c r="AY148" t="n">
+        <v>147</v>
+      </c>
+      <c r="AZ148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA148" t="n">
+        <v>0</v>
+      </c>
       <c r="BB148" t="inlineStr"/>
       <c r="BC148" t="inlineStr">
         <is>
@@ -24909,9 +25791,15 @@
         <v>0</v>
       </c>
       <c r="AX149" t="inlineStr"/>
-      <c r="AY149" t="inlineStr"/>
-      <c r="AZ149" t="inlineStr"/>
-      <c r="BA149" t="inlineStr"/>
+      <c r="AY149" t="n">
+        <v>148</v>
+      </c>
+      <c r="AZ149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA149" t="n">
+        <v>0</v>
+      </c>
       <c r="BB149" t="inlineStr"/>
       <c r="BC149" t="inlineStr">
         <is>
@@ -25066,9 +25954,15 @@
         <v>0</v>
       </c>
       <c r="AX150" t="inlineStr"/>
-      <c r="AY150" t="inlineStr"/>
-      <c r="AZ150" t="inlineStr"/>
-      <c r="BA150" t="inlineStr"/>
+      <c r="AY150" t="n">
+        <v>149</v>
+      </c>
+      <c r="AZ150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA150" t="n">
+        <v>0</v>
+      </c>
       <c r="BB150" t="inlineStr"/>
       <c r="BC150" t="inlineStr">
         <is>
@@ -25227,9 +26121,15 @@
         <v>0</v>
       </c>
       <c r="AX151" t="inlineStr"/>
-      <c r="AY151" t="inlineStr"/>
-      <c r="AZ151" t="inlineStr"/>
-      <c r="BA151" t="inlineStr"/>
+      <c r="AY151" t="n">
+        <v>150</v>
+      </c>
+      <c r="AZ151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA151" t="n">
+        <v>0</v>
+      </c>
       <c r="BB151" t="inlineStr"/>
       <c r="BC151" t="inlineStr">
         <is>
@@ -25386,9 +26286,15 @@
         <v>0</v>
       </c>
       <c r="AX152" t="inlineStr"/>
-      <c r="AY152" t="inlineStr"/>
-      <c r="AZ152" t="inlineStr"/>
-      <c r="BA152" t="inlineStr"/>
+      <c r="AY152" t="n">
+        <v>151</v>
+      </c>
+      <c r="AZ152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA152" t="n">
+        <v>0</v>
+      </c>
       <c r="BB152" t="inlineStr"/>
       <c r="BC152" t="inlineStr">
         <is>
@@ -25549,9 +26455,15 @@
         <v>0</v>
       </c>
       <c r="AX153" t="inlineStr"/>
-      <c r="AY153" t="inlineStr"/>
-      <c r="AZ153" t="inlineStr"/>
-      <c r="BA153" t="inlineStr"/>
+      <c r="AY153" t="n">
+        <v>152</v>
+      </c>
+      <c r="AZ153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA153" t="n">
+        <v>0</v>
+      </c>
       <c r="BB153" t="inlineStr"/>
       <c r="BC153" t="inlineStr">
         <is>
@@ -25710,9 +26622,15 @@
         <v>0</v>
       </c>
       <c r="AX154" t="inlineStr"/>
-      <c r="AY154" t="inlineStr"/>
-      <c r="AZ154" t="inlineStr"/>
-      <c r="BA154" t="inlineStr"/>
+      <c r="AY154" t="n">
+        <v>153</v>
+      </c>
+      <c r="AZ154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA154" t="n">
+        <v>0</v>
+      </c>
       <c r="BB154" t="inlineStr"/>
       <c r="BC154" t="inlineStr">
         <is>
@@ -25871,9 +26789,15 @@
         <v>0</v>
       </c>
       <c r="AX155" t="inlineStr"/>
-      <c r="AY155" t="inlineStr"/>
-      <c r="AZ155" t="inlineStr"/>
-      <c r="BA155" t="inlineStr"/>
+      <c r="AY155" t="n">
+        <v>154</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA155" t="n">
+        <v>0</v>
+      </c>
       <c r="BB155" t="inlineStr"/>
       <c r="BC155" t="inlineStr">
         <is>
@@ -26030,9 +26954,15 @@
         <v>0</v>
       </c>
       <c r="AX156" t="inlineStr"/>
-      <c r="AY156" t="inlineStr"/>
-      <c r="AZ156" t="inlineStr"/>
-      <c r="BA156" t="inlineStr"/>
+      <c r="AY156" t="n">
+        <v>155</v>
+      </c>
+      <c r="AZ156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA156" t="n">
+        <v>0</v>
+      </c>
       <c r="BB156" t="inlineStr"/>
       <c r="BC156" t="inlineStr">
         <is>
@@ -26187,9 +27117,15 @@
         <v>0</v>
       </c>
       <c r="AX157" t="inlineStr"/>
-      <c r="AY157" t="inlineStr"/>
-      <c r="AZ157" t="inlineStr"/>
-      <c r="BA157" t="inlineStr"/>
+      <c r="AY157" t="n">
+        <v>156</v>
+      </c>
+      <c r="AZ157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA157" t="n">
+        <v>0</v>
+      </c>
       <c r="BB157" t="inlineStr"/>
       <c r="BC157" t="inlineStr">
         <is>
@@ -26346,9 +27282,15 @@
         <v>0</v>
       </c>
       <c r="AX158" t="inlineStr"/>
-      <c r="AY158" t="inlineStr"/>
-      <c r="AZ158" t="inlineStr"/>
-      <c r="BA158" t="inlineStr"/>
+      <c r="AY158" t="n">
+        <v>157</v>
+      </c>
+      <c r="AZ158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA158" t="n">
+        <v>0</v>
+      </c>
       <c r="BB158" t="inlineStr"/>
       <c r="BC158" t="inlineStr">
         <is>
@@ -26507,9 +27449,15 @@
         <v>0</v>
       </c>
       <c r="AX159" t="inlineStr"/>
-      <c r="AY159" t="inlineStr"/>
-      <c r="AZ159" t="inlineStr"/>
-      <c r="BA159" t="inlineStr"/>
+      <c r="AY159" t="n">
+        <v>158</v>
+      </c>
+      <c r="AZ159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA159" t="n">
+        <v>0</v>
+      </c>
       <c r="BB159" t="inlineStr"/>
       <c r="BC159" t="inlineStr">
         <is>
@@ -26668,9 +27616,15 @@
         <v>0</v>
       </c>
       <c r="AX160" t="inlineStr"/>
-      <c r="AY160" t="inlineStr"/>
-      <c r="AZ160" t="inlineStr"/>
-      <c r="BA160" t="inlineStr"/>
+      <c r="AY160" t="n">
+        <v>159</v>
+      </c>
+      <c r="AZ160" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA160" t="n">
+        <v>0</v>
+      </c>
       <c r="BB160" t="inlineStr"/>
       <c r="BC160" t="inlineStr">
         <is>
@@ -26829,9 +27783,15 @@
         <v>0</v>
       </c>
       <c r="AX161" t="inlineStr"/>
-      <c r="AY161" t="inlineStr"/>
-      <c r="AZ161" t="inlineStr"/>
-      <c r="BA161" t="inlineStr"/>
+      <c r="AY161" t="n">
+        <v>160</v>
+      </c>
+      <c r="AZ161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA161" t="n">
+        <v>0</v>
+      </c>
       <c r="BB161" t="inlineStr"/>
       <c r="BC161" t="inlineStr">
         <is>
@@ -26990,9 +27950,15 @@
         <v>0</v>
       </c>
       <c r="AX162" t="inlineStr"/>
-      <c r="AY162" t="inlineStr"/>
-      <c r="AZ162" t="inlineStr"/>
-      <c r="BA162" t="inlineStr"/>
+      <c r="AY162" t="n">
+        <v>161</v>
+      </c>
+      <c r="AZ162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA162" t="n">
+        <v>0</v>
+      </c>
       <c r="BB162" t="inlineStr"/>
       <c r="BC162" t="inlineStr">
         <is>
@@ -27149,9 +28115,15 @@
         <v>0</v>
       </c>
       <c r="AX163" t="inlineStr"/>
-      <c r="AY163" t="inlineStr"/>
-      <c r="AZ163" t="inlineStr"/>
-      <c r="BA163" t="inlineStr"/>
+      <c r="AY163" t="n">
+        <v>162</v>
+      </c>
+      <c r="AZ163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA163" t="n">
+        <v>0</v>
+      </c>
       <c r="BB163" t="inlineStr"/>
       <c r="BC163" t="inlineStr">
         <is>
@@ -27314,9 +28286,15 @@
         <v>0</v>
       </c>
       <c r="AX164" t="inlineStr"/>
-      <c r="AY164" t="inlineStr"/>
-      <c r="AZ164" t="inlineStr"/>
-      <c r="BA164" t="inlineStr"/>
+      <c r="AY164" t="n">
+        <v>163</v>
+      </c>
+      <c r="AZ164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA164" t="n">
+        <v>0</v>
+      </c>
       <c r="BB164" t="inlineStr"/>
       <c r="BC164" t="inlineStr">
         <is>
@@ -27475,9 +28453,15 @@
         <v>0</v>
       </c>
       <c r="AX165" t="inlineStr"/>
-      <c r="AY165" t="inlineStr"/>
-      <c r="AZ165" t="inlineStr"/>
-      <c r="BA165" t="inlineStr"/>
+      <c r="AY165" t="n">
+        <v>164</v>
+      </c>
+      <c r="AZ165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA165" t="n">
+        <v>0</v>
+      </c>
       <c r="BB165" t="inlineStr"/>
       <c r="BC165" t="inlineStr">
         <is>
@@ -27640,9 +28624,15 @@
         <v>0</v>
       </c>
       <c r="AX166" t="inlineStr"/>
-      <c r="AY166" t="inlineStr"/>
-      <c r="AZ166" t="inlineStr"/>
-      <c r="BA166" t="inlineStr"/>
+      <c r="AY166" t="n">
+        <v>165</v>
+      </c>
+      <c r="AZ166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA166" t="n">
+        <v>0</v>
+      </c>
       <c r="BB166" t="inlineStr"/>
       <c r="BC166" t="inlineStr">
         <is>
@@ -27801,9 +28791,15 @@
         <v>0</v>
       </c>
       <c r="AX167" t="inlineStr"/>
-      <c r="AY167" t="inlineStr"/>
-      <c r="AZ167" t="inlineStr"/>
-      <c r="BA167" t="inlineStr"/>
+      <c r="AY167" t="n">
+        <v>166</v>
+      </c>
+      <c r="AZ167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA167" t="n">
+        <v>0</v>
+      </c>
       <c r="BB167" t="inlineStr"/>
       <c r="BC167" t="inlineStr">
         <is>
@@ -27962,9 +28958,15 @@
         <v>0</v>
       </c>
       <c r="AX168" t="inlineStr"/>
-      <c r="AY168" t="inlineStr"/>
-      <c r="AZ168" t="inlineStr"/>
-      <c r="BA168" t="inlineStr"/>
+      <c r="AY168" t="n">
+        <v>167</v>
+      </c>
+      <c r="AZ168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA168" t="n">
+        <v>0</v>
+      </c>
       <c r="BB168" t="inlineStr"/>
       <c r="BC168" t="inlineStr">
         <is>
@@ -28121,9 +29123,15 @@
         <v>0</v>
       </c>
       <c r="AX169" t="inlineStr"/>
-      <c r="AY169" t="inlineStr"/>
-      <c r="AZ169" t="inlineStr"/>
-      <c r="BA169" t="inlineStr"/>
+      <c r="AY169" t="n">
+        <v>168</v>
+      </c>
+      <c r="AZ169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA169" t="n">
+        <v>0</v>
+      </c>
       <c r="BB169" t="inlineStr"/>
       <c r="BC169" t="inlineStr">
         <is>
@@ -28282,9 +29290,15 @@
         <v>0</v>
       </c>
       <c r="AX170" t="inlineStr"/>
-      <c r="AY170" t="inlineStr"/>
-      <c r="AZ170" t="inlineStr"/>
-      <c r="BA170" t="inlineStr"/>
+      <c r="AY170" t="n">
+        <v>169</v>
+      </c>
+      <c r="AZ170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA170" t="n">
+        <v>0</v>
+      </c>
       <c r="BB170" t="inlineStr"/>
       <c r="BC170" t="inlineStr">
         <is>
@@ -28443,9 +29457,15 @@
         <v>0</v>
       </c>
       <c r="AX171" t="inlineStr"/>
-      <c r="AY171" t="inlineStr"/>
-      <c r="AZ171" t="inlineStr"/>
-      <c r="BA171" t="inlineStr"/>
+      <c r="AY171" t="n">
+        <v>170</v>
+      </c>
+      <c r="AZ171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA171" t="n">
+        <v>0</v>
+      </c>
       <c r="BB171" t="inlineStr"/>
       <c r="BC171" t="inlineStr">
         <is>
@@ -28604,9 +29624,15 @@
         <v>0</v>
       </c>
       <c r="AX172" t="inlineStr"/>
-      <c r="AY172" t="inlineStr"/>
-      <c r="AZ172" t="inlineStr"/>
-      <c r="BA172" t="inlineStr"/>
+      <c r="AY172" t="n">
+        <v>171</v>
+      </c>
+      <c r="AZ172" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA172" t="n">
+        <v>0</v>
+      </c>
       <c r="BB172" t="inlineStr"/>
       <c r="BC172" t="inlineStr">
         <is>
@@ -28769,9 +29795,15 @@
         <v>0</v>
       </c>
       <c r="AX173" t="inlineStr"/>
-      <c r="AY173" t="inlineStr"/>
-      <c r="AZ173" t="inlineStr"/>
-      <c r="BA173" t="inlineStr"/>
+      <c r="AY173" t="n">
+        <v>172</v>
+      </c>
+      <c r="AZ173" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA173" t="n">
+        <v>0</v>
+      </c>
       <c r="BB173" t="inlineStr"/>
       <c r="BC173" t="inlineStr">
         <is>
@@ -28930,9 +29962,15 @@
         <v>0</v>
       </c>
       <c r="AX174" t="inlineStr"/>
-      <c r="AY174" t="inlineStr"/>
-      <c r="AZ174" t="inlineStr"/>
-      <c r="BA174" t="inlineStr"/>
+      <c r="AY174" t="n">
+        <v>173</v>
+      </c>
+      <c r="AZ174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA174" t="n">
+        <v>0</v>
+      </c>
       <c r="BB174" t="inlineStr"/>
       <c r="BC174" t="inlineStr">
         <is>
@@ -29091,9 +30129,15 @@
         <v>0</v>
       </c>
       <c r="AX175" t="inlineStr"/>
-      <c r="AY175" t="inlineStr"/>
-      <c r="AZ175" t="inlineStr"/>
-      <c r="BA175" t="inlineStr"/>
+      <c r="AY175" t="n">
+        <v>174</v>
+      </c>
+      <c r="AZ175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA175" t="n">
+        <v>0</v>
+      </c>
       <c r="BB175" t="inlineStr"/>
       <c r="BC175" t="inlineStr">
         <is>
@@ -29242,9 +30286,15 @@
         <v>0</v>
       </c>
       <c r="AX176" t="inlineStr"/>
-      <c r="AY176" t="inlineStr"/>
-      <c r="AZ176" t="inlineStr"/>
-      <c r="BA176" t="inlineStr"/>
+      <c r="AY176" t="n">
+        <v>175</v>
+      </c>
+      <c r="AZ176" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA176" t="n">
+        <v>0</v>
+      </c>
       <c r="BB176" t="inlineStr"/>
       <c r="BC176" t="inlineStr">
         <is>
@@ -29399,9 +30449,15 @@
         <v>0</v>
       </c>
       <c r="AX177" t="inlineStr"/>
-      <c r="AY177" t="inlineStr"/>
-      <c r="AZ177" t="inlineStr"/>
-      <c r="BA177" t="inlineStr"/>
+      <c r="AY177" t="n">
+        <v>176</v>
+      </c>
+      <c r="AZ177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA177" t="n">
+        <v>0</v>
+      </c>
       <c r="BB177" t="inlineStr"/>
       <c r="BC177" t="inlineStr">
         <is>
@@ -29560,9 +30616,15 @@
         <v>0</v>
       </c>
       <c r="AX178" t="inlineStr"/>
-      <c r="AY178" t="inlineStr"/>
-      <c r="AZ178" t="inlineStr"/>
-      <c r="BA178" t="inlineStr"/>
+      <c r="AY178" t="n">
+        <v>177</v>
+      </c>
+      <c r="AZ178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA178" t="n">
+        <v>0</v>
+      </c>
       <c r="BB178" t="inlineStr"/>
       <c r="BC178" t="inlineStr">
         <is>
@@ -29721,9 +30783,15 @@
         <v>0</v>
       </c>
       <c r="AX179" t="inlineStr"/>
-      <c r="AY179" t="inlineStr"/>
-      <c r="AZ179" t="inlineStr"/>
-      <c r="BA179" t="inlineStr"/>
+      <c r="AY179" t="n">
+        <v>178</v>
+      </c>
+      <c r="AZ179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA179" t="n">
+        <v>0</v>
+      </c>
       <c r="BB179" t="inlineStr"/>
       <c r="BC179" t="inlineStr">
         <is>
@@ -29882,9 +30950,15 @@
         <v>0</v>
       </c>
       <c r="AX180" t="inlineStr"/>
-      <c r="AY180" t="inlineStr"/>
-      <c r="AZ180" t="inlineStr"/>
-      <c r="BA180" t="inlineStr"/>
+      <c r="AY180" t="n">
+        <v>179</v>
+      </c>
+      <c r="AZ180" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA180" t="n">
+        <v>0</v>
+      </c>
       <c r="BB180" t="inlineStr"/>
       <c r="BC180" t="inlineStr">
         <is>
@@ -30043,9 +31117,15 @@
         <v>0</v>
       </c>
       <c r="AX181" t="inlineStr"/>
-      <c r="AY181" t="inlineStr"/>
-      <c r="AZ181" t="inlineStr"/>
-      <c r="BA181" t="inlineStr"/>
+      <c r="AY181" t="n">
+        <v>180</v>
+      </c>
+      <c r="AZ181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA181" t="n">
+        <v>0</v>
+      </c>
       <c r="BB181" t="inlineStr"/>
       <c r="BC181" t="inlineStr">
         <is>
@@ -30202,9 +31282,15 @@
         <v>0</v>
       </c>
       <c r="AX182" t="inlineStr"/>
-      <c r="AY182" t="inlineStr"/>
-      <c r="AZ182" t="inlineStr"/>
-      <c r="BA182" t="inlineStr"/>
+      <c r="AY182" t="n">
+        <v>181</v>
+      </c>
+      <c r="AZ182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA182" t="n">
+        <v>0</v>
+      </c>
       <c r="BB182" t="inlineStr"/>
       <c r="BC182" t="inlineStr">
         <is>
@@ -30361,9 +31447,15 @@
         <v>0</v>
       </c>
       <c r="AX183" t="inlineStr"/>
-      <c r="AY183" t="inlineStr"/>
-      <c r="AZ183" t="inlineStr"/>
-      <c r="BA183" t="inlineStr"/>
+      <c r="AY183" t="n">
+        <v>182</v>
+      </c>
+      <c r="AZ183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA183" t="n">
+        <v>0</v>
+      </c>
       <c r="BB183" t="inlineStr"/>
       <c r="BC183" t="inlineStr">
         <is>
@@ -30522,9 +31614,15 @@
         <v>0</v>
       </c>
       <c r="AX184" t="inlineStr"/>
-      <c r="AY184" t="inlineStr"/>
-      <c r="AZ184" t="inlineStr"/>
-      <c r="BA184" t="inlineStr"/>
+      <c r="AY184" t="n">
+        <v>183</v>
+      </c>
+      <c r="AZ184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA184" t="n">
+        <v>0</v>
+      </c>
       <c r="BB184" t="inlineStr"/>
       <c r="BC184" t="inlineStr">
         <is>
@@ -30681,9 +31779,15 @@
         <v>0</v>
       </c>
       <c r="AX185" t="inlineStr"/>
-      <c r="AY185" t="inlineStr"/>
-      <c r="AZ185" t="inlineStr"/>
-      <c r="BA185" t="inlineStr"/>
+      <c r="AY185" t="n">
+        <v>184</v>
+      </c>
+      <c r="AZ185" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA185" t="n">
+        <v>0</v>
+      </c>
       <c r="BB185" t="inlineStr"/>
       <c r="BC185" t="inlineStr">
         <is>
@@ -30842,9 +31946,15 @@
         <v>0</v>
       </c>
       <c r="AX186" t="inlineStr"/>
-      <c r="AY186" t="inlineStr"/>
-      <c r="AZ186" t="inlineStr"/>
-      <c r="BA186" t="inlineStr"/>
+      <c r="AY186" t="n">
+        <v>185</v>
+      </c>
+      <c r="AZ186" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA186" t="n">
+        <v>0</v>
+      </c>
       <c r="BB186" t="inlineStr"/>
       <c r="BC186" t="inlineStr">
         <is>
@@ -31005,9 +32115,15 @@
         <v>0</v>
       </c>
       <c r="AX187" t="inlineStr"/>
-      <c r="AY187" t="inlineStr"/>
-      <c r="AZ187" t="inlineStr"/>
-      <c r="BA187" t="inlineStr"/>
+      <c r="AY187" t="n">
+        <v>186</v>
+      </c>
+      <c r="AZ187" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA187" t="n">
+        <v>0</v>
+      </c>
       <c r="BB187" t="inlineStr"/>
       <c r="BC187" t="inlineStr">
         <is>
@@ -31160,9 +32276,15 @@
         <v>0</v>
       </c>
       <c r="AX188" t="inlineStr"/>
-      <c r="AY188" t="inlineStr"/>
-      <c r="AZ188" t="inlineStr"/>
-      <c r="BA188" t="inlineStr"/>
+      <c r="AY188" t="n">
+        <v>187</v>
+      </c>
+      <c r="AZ188" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA188" t="n">
+        <v>0</v>
+      </c>
       <c r="BB188" t="inlineStr"/>
       <c r="BC188" t="inlineStr">
         <is>
@@ -31321,9 +32443,15 @@
         <v>0</v>
       </c>
       <c r="AX189" t="inlineStr"/>
-      <c r="AY189" t="inlineStr"/>
-      <c r="AZ189" t="inlineStr"/>
-      <c r="BA189" t="inlineStr"/>
+      <c r="AY189" t="n">
+        <v>188</v>
+      </c>
+      <c r="AZ189" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA189" t="n">
+        <v>0</v>
+      </c>
       <c r="BB189" t="inlineStr"/>
       <c r="BC189" t="inlineStr">
         <is>
@@ -31480,9 +32608,15 @@
         <v>0</v>
       </c>
       <c r="AX190" t="inlineStr"/>
-      <c r="AY190" t="inlineStr"/>
-      <c r="AZ190" t="inlineStr"/>
-      <c r="BA190" t="inlineStr"/>
+      <c r="AY190" t="n">
+        <v>189</v>
+      </c>
+      <c r="AZ190" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA190" t="n">
+        <v>0</v>
+      </c>
       <c r="BB190" t="inlineStr"/>
       <c r="BC190" t="inlineStr">
         <is>
@@ -31639,9 +32773,15 @@
         <v>0</v>
       </c>
       <c r="AX191" t="inlineStr"/>
-      <c r="AY191" t="inlineStr"/>
-      <c r="AZ191" t="inlineStr"/>
-      <c r="BA191" t="inlineStr"/>
+      <c r="AY191" t="n">
+        <v>190</v>
+      </c>
+      <c r="AZ191" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA191" t="n">
+        <v>0</v>
+      </c>
       <c r="BB191" t="inlineStr"/>
       <c r="BC191" t="inlineStr">
         <is>
@@ -31798,9 +32938,15 @@
         <v>0</v>
       </c>
       <c r="AX192" t="inlineStr"/>
-      <c r="AY192" t="inlineStr"/>
-      <c r="AZ192" t="inlineStr"/>
-      <c r="BA192" t="inlineStr"/>
+      <c r="AY192" t="n">
+        <v>191</v>
+      </c>
+      <c r="AZ192" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA192" t="n">
+        <v>0</v>
+      </c>
       <c r="BB192" t="inlineStr"/>
       <c r="BC192" t="inlineStr">
         <is>
@@ -31957,9 +33103,15 @@
         <v>0</v>
       </c>
       <c r="AX193" t="inlineStr"/>
-      <c r="AY193" t="inlineStr"/>
-      <c r="AZ193" t="inlineStr"/>
-      <c r="BA193" t="inlineStr"/>
+      <c r="AY193" t="n">
+        <v>192</v>
+      </c>
+      <c r="AZ193" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA193" t="n">
+        <v>0</v>
+      </c>
       <c r="BB193" t="inlineStr"/>
       <c r="BC193" t="inlineStr">
         <is>
@@ -32116,9 +33268,15 @@
         <v>0</v>
       </c>
       <c r="AX194" t="inlineStr"/>
-      <c r="AY194" t="inlineStr"/>
-      <c r="AZ194" t="inlineStr"/>
-      <c r="BA194" t="inlineStr"/>
+      <c r="AY194" t="n">
+        <v>193</v>
+      </c>
+      <c r="AZ194" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA194" t="n">
+        <v>0</v>
+      </c>
       <c r="BB194" t="inlineStr"/>
       <c r="BC194" t="inlineStr">
         <is>
@@ -32275,9 +33433,15 @@
         <v>0</v>
       </c>
       <c r="AX195" t="inlineStr"/>
-      <c r="AY195" t="inlineStr"/>
-      <c r="AZ195" t="inlineStr"/>
-      <c r="BA195" t="inlineStr"/>
+      <c r="AY195" t="n">
+        <v>194</v>
+      </c>
+      <c r="AZ195" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA195" t="n">
+        <v>0</v>
+      </c>
       <c r="BB195" t="inlineStr"/>
       <c r="BC195" t="inlineStr">
         <is>
@@ -32432,9 +33596,15 @@
         <v>0</v>
       </c>
       <c r="AX196" t="inlineStr"/>
-      <c r="AY196" t="inlineStr"/>
-      <c r="AZ196" t="inlineStr"/>
-      <c r="BA196" t="inlineStr"/>
+      <c r="AY196" t="n">
+        <v>195</v>
+      </c>
+      <c r="AZ196" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA196" t="n">
+        <v>0</v>
+      </c>
       <c r="BB196" t="inlineStr"/>
       <c r="BC196" t="inlineStr">
         <is>
@@ -32587,9 +33757,15 @@
         <v>0</v>
       </c>
       <c r="AX197" t="inlineStr"/>
-      <c r="AY197" t="inlineStr"/>
-      <c r="AZ197" t="inlineStr"/>
-      <c r="BA197" t="inlineStr"/>
+      <c r="AY197" t="n">
+        <v>196</v>
+      </c>
+      <c r="AZ197" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA197" t="n">
+        <v>0</v>
+      </c>
       <c r="BB197" t="inlineStr"/>
       <c r="BC197" t="inlineStr">
         <is>
@@ -32744,9 +33920,15 @@
         <v>0</v>
       </c>
       <c r="AX198" t="inlineStr"/>
-      <c r="AY198" t="inlineStr"/>
-      <c r="AZ198" t="inlineStr"/>
-      <c r="BA198" t="inlineStr"/>
+      <c r="AY198" t="n">
+        <v>197</v>
+      </c>
+      <c r="AZ198" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA198" t="n">
+        <v>0</v>
+      </c>
       <c r="BB198" t="inlineStr"/>
       <c r="BC198" t="inlineStr">
         <is>
@@ -32905,9 +34087,15 @@
         <v>0</v>
       </c>
       <c r="AX199" t="inlineStr"/>
-      <c r="AY199" t="inlineStr"/>
-      <c r="AZ199" t="inlineStr"/>
-      <c r="BA199" t="inlineStr"/>
+      <c r="AY199" t="n">
+        <v>198</v>
+      </c>
+      <c r="AZ199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA199" t="n">
+        <v>0</v>
+      </c>
       <c r="BB199" t="inlineStr"/>
       <c r="BC199" t="inlineStr">
         <is>
@@ -33064,9 +34252,15 @@
         <v>0</v>
       </c>
       <c r="AX200" t="inlineStr"/>
-      <c r="AY200" t="inlineStr"/>
-      <c r="AZ200" t="inlineStr"/>
-      <c r="BA200" t="inlineStr"/>
+      <c r="AY200" t="n">
+        <v>199</v>
+      </c>
+      <c r="AZ200" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA200" t="n">
+        <v>0</v>
+      </c>
       <c r="BB200" t="inlineStr"/>
       <c r="BC200" t="inlineStr">
         <is>
@@ -33223,9 +34417,15 @@
         <v>0</v>
       </c>
       <c r="AX201" t="inlineStr"/>
-      <c r="AY201" t="inlineStr"/>
-      <c r="AZ201" t="inlineStr"/>
-      <c r="BA201" t="inlineStr"/>
+      <c r="AY201" t="n">
+        <v>200</v>
+      </c>
+      <c r="AZ201" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA201" t="n">
+        <v>0</v>
+      </c>
       <c r="BB201" t="inlineStr"/>
       <c r="BC201" t="inlineStr">
         <is>
@@ -33384,9 +34584,15 @@
         <v>0</v>
       </c>
       <c r="AX202" t="inlineStr"/>
-      <c r="AY202" t="inlineStr"/>
-      <c r="AZ202" t="inlineStr"/>
-      <c r="BA202" t="inlineStr"/>
+      <c r="AY202" t="n">
+        <v>201</v>
+      </c>
+      <c r="AZ202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA202" t="n">
+        <v>0</v>
+      </c>
       <c r="BB202" t="inlineStr"/>
       <c r="BC202" t="inlineStr">
         <is>
@@ -33545,9 +34751,15 @@
         <v>0</v>
       </c>
       <c r="AX203" t="inlineStr"/>
-      <c r="AY203" t="inlineStr"/>
-      <c r="AZ203" t="inlineStr"/>
-      <c r="BA203" t="inlineStr"/>
+      <c r="AY203" t="n">
+        <v>202</v>
+      </c>
+      <c r="AZ203" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA203" t="n">
+        <v>0</v>
+      </c>
       <c r="BB203" t="inlineStr"/>
       <c r="BC203" t="inlineStr">
         <is>
@@ -33704,9 +34916,15 @@
         <v>0</v>
       </c>
       <c r="AX204" t="inlineStr"/>
-      <c r="AY204" t="inlineStr"/>
-      <c r="AZ204" t="inlineStr"/>
-      <c r="BA204" t="inlineStr"/>
+      <c r="AY204" t="n">
+        <v>203</v>
+      </c>
+      <c r="AZ204" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA204" t="n">
+        <v>0</v>
+      </c>
       <c r="BB204" t="inlineStr"/>
       <c r="BC204" t="inlineStr">
         <is>
@@ -33758,7 +34976,7 @@
         <v>33.9</v>
       </c>
       <c r="K205" t="n">
-        <v>13.4</v>
+        <v>14.7</v>
       </c>
       <c r="L205" t="n">
         <v>33.9</v>
@@ -33865,9 +35083,15 @@
         <v>0</v>
       </c>
       <c r="AX205" t="inlineStr"/>
-      <c r="AY205" t="inlineStr"/>
-      <c r="AZ205" t="inlineStr"/>
-      <c r="BA205" t="inlineStr"/>
+      <c r="AY205" t="n">
+        <v>204</v>
+      </c>
+      <c r="AZ205" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA205" t="n">
+        <v>0</v>
+      </c>
       <c r="BB205" t="inlineStr"/>
       <c r="BC205" t="inlineStr">
         <is>
@@ -34026,9 +35250,15 @@
         <v>0</v>
       </c>
       <c r="AX206" t="inlineStr"/>
-      <c r="AY206" t="inlineStr"/>
-      <c r="AZ206" t="inlineStr"/>
-      <c r="BA206" t="inlineStr"/>
+      <c r="AY206" t="n">
+        <v>205</v>
+      </c>
+      <c r="AZ206" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA206" t="n">
+        <v>0</v>
+      </c>
       <c r="BB206" t="inlineStr"/>
       <c r="BC206" t="inlineStr">
         <is>
@@ -34187,9 +35417,15 @@
         <v>0</v>
       </c>
       <c r="AX207" t="inlineStr"/>
-      <c r="AY207" t="inlineStr"/>
-      <c r="AZ207" t="inlineStr"/>
-      <c r="BA207" t="inlineStr"/>
+      <c r="AY207" t="n">
+        <v>206</v>
+      </c>
+      <c r="AZ207" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA207" t="n">
+        <v>0</v>
+      </c>
       <c r="BB207" t="inlineStr"/>
       <c r="BC207" t="inlineStr">
         <is>
@@ -34348,9 +35584,15 @@
         <v>0</v>
       </c>
       <c r="AX208" t="inlineStr"/>
-      <c r="AY208" t="inlineStr"/>
-      <c r="AZ208" t="inlineStr"/>
-      <c r="BA208" t="inlineStr"/>
+      <c r="AY208" t="n">
+        <v>207</v>
+      </c>
+      <c r="AZ208" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA208" t="n">
+        <v>0</v>
+      </c>
       <c r="BB208" t="inlineStr"/>
       <c r="BC208" t="inlineStr">
         <is>
@@ -34505,9 +35747,15 @@
         <v>0</v>
       </c>
       <c r="AX209" t="inlineStr"/>
-      <c r="AY209" t="inlineStr"/>
-      <c r="AZ209" t="inlineStr"/>
-      <c r="BA209" t="inlineStr"/>
+      <c r="AY209" t="n">
+        <v>208</v>
+      </c>
+      <c r="AZ209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA209" t="n">
+        <v>0</v>
+      </c>
       <c r="BB209" t="inlineStr"/>
       <c r="BC209" t="inlineStr">
         <is>
@@ -34666,9 +35914,15 @@
         <v>0</v>
       </c>
       <c r="AX210" t="inlineStr"/>
-      <c r="AY210" t="inlineStr"/>
-      <c r="AZ210" t="inlineStr"/>
-      <c r="BA210" t="inlineStr"/>
+      <c r="AY210" t="n">
+        <v>209</v>
+      </c>
+      <c r="AZ210" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA210" t="n">
+        <v>0</v>
+      </c>
       <c r="BB210" t="inlineStr"/>
       <c r="BC210" t="inlineStr">
         <is>
@@ -34825,9 +36079,15 @@
         <v>0</v>
       </c>
       <c r="AX211" t="inlineStr"/>
-      <c r="AY211" t="inlineStr"/>
-      <c r="AZ211" t="inlineStr"/>
-      <c r="BA211" t="inlineStr"/>
+      <c r="AY211" t="n">
+        <v>210</v>
+      </c>
+      <c r="AZ211" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA211" t="n">
+        <v>0</v>
+      </c>
       <c r="BB211" t="inlineStr"/>
       <c r="BC211" t="inlineStr">
         <is>
@@ -34980,9 +36240,15 @@
         <v>0</v>
       </c>
       <c r="AX212" t="inlineStr"/>
-      <c r="AY212" t="inlineStr"/>
-      <c r="AZ212" t="inlineStr"/>
-      <c r="BA212" t="inlineStr"/>
+      <c r="AY212" t="n">
+        <v>211</v>
+      </c>
+      <c r="AZ212" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA212" t="n">
+        <v>0</v>
+      </c>
       <c r="BB212" t="inlineStr"/>
       <c r="BC212" t="inlineStr">
         <is>
@@ -35135,9 +36401,15 @@
         <v>0</v>
       </c>
       <c r="AX213" t="inlineStr"/>
-      <c r="AY213" t="inlineStr"/>
-      <c r="AZ213" t="inlineStr"/>
-      <c r="BA213" t="inlineStr"/>
+      <c r="AY213" t="n">
+        <v>212</v>
+      </c>
+      <c r="AZ213" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA213" t="n">
+        <v>0</v>
+      </c>
       <c r="BB213" t="inlineStr"/>
       <c r="BC213" t="inlineStr">
         <is>
@@ -35294,9 +36566,15 @@
         <v>0</v>
       </c>
       <c r="AX214" t="inlineStr"/>
-      <c r="AY214" t="inlineStr"/>
-      <c r="AZ214" t="inlineStr"/>
-      <c r="BA214" t="inlineStr"/>
+      <c r="AY214" t="n">
+        <v>213</v>
+      </c>
+      <c r="AZ214" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA214" t="n">
+        <v>0</v>
+      </c>
       <c r="BB214" t="inlineStr"/>
       <c r="BC214" t="inlineStr">
         <is>
@@ -35449,9 +36727,15 @@
         <v>0</v>
       </c>
       <c r="AX215" t="inlineStr"/>
-      <c r="AY215" t="inlineStr"/>
-      <c r="AZ215" t="inlineStr"/>
-      <c r="BA215" t="inlineStr"/>
+      <c r="AY215" t="n">
+        <v>214</v>
+      </c>
+      <c r="AZ215" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA215" t="n">
+        <v>0</v>
+      </c>
       <c r="BB215" t="inlineStr"/>
       <c r="BC215" t="inlineStr">
         <is>
@@ -35610,9 +36894,15 @@
         <v>0</v>
       </c>
       <c r="AX216" t="inlineStr"/>
-      <c r="AY216" t="inlineStr"/>
-      <c r="AZ216" t="inlineStr"/>
-      <c r="BA216" t="inlineStr"/>
+      <c r="AY216" t="n">
+        <v>215</v>
+      </c>
+      <c r="AZ216" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA216" t="n">
+        <v>0</v>
+      </c>
       <c r="BB216" t="inlineStr"/>
       <c r="BC216" t="inlineStr">
         <is>
@@ -35769,9 +37059,15 @@
         <v>0</v>
       </c>
       <c r="AX217" t="inlineStr"/>
-      <c r="AY217" t="inlineStr"/>
-      <c r="AZ217" t="inlineStr"/>
-      <c r="BA217" t="inlineStr"/>
+      <c r="AY217" t="n">
+        <v>216</v>
+      </c>
+      <c r="AZ217" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA217" t="n">
+        <v>0</v>
+      </c>
       <c r="BB217" t="inlineStr"/>
       <c r="BC217" t="inlineStr">
         <is>
@@ -36231,7 +37527,7 @@
         <v>1734</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -36239,9 +37535,15 @@
       <c r="AX2" t="n">
         <v>0</v>
       </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
+      <c r="AY2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
       <c r="BB2" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -36410,7 +37712,7 @@
         <v>2081</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -36418,9 +37720,15 @@
       <c r="AX3" t="n">
         <v>0</v>
       </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
+      <c r="AY3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
       <c r="BB3" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -36589,7 +37897,7 @@
         <v>1554</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
@@ -36597,9 +37905,15 @@
       <c r="AX4" t="n">
         <v>0</v>
       </c>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
+      <c r="AY4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
       <c r="BB4" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -36772,7 +38086,7 @@
         <v>1841.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
@@ -36780,9 +38094,15 @@
       <c r="AX5" t="n">
         <v>0</v>
       </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
+      <c r="AY5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
       <c r="BB5" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -36951,7 +38271,7 @@
         <v>1771</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
@@ -36959,9 +38279,15 @@
       <c r="AX6" t="n">
         <v>0</v>
       </c>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
+      <c r="AY6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
       <c r="BB6" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -37130,7 +38456,7 @@
         <v>7647</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
@@ -37138,9 +38464,15 @@
       <c r="AX7" t="n">
         <v>0</v>
       </c>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="inlineStr"/>
+      <c r="AY7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
       <c r="BB7" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -37309,7 +38641,7 @@
         <v>497.9</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
@@ -37317,9 +38649,15 @@
       <c r="AX8" t="n">
         <v>0</v>
       </c>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="inlineStr"/>
+      <c r="AY8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
       <c r="BB8" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -37488,7 +38826,7 @@
         <v>5495</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
@@ -37496,9 +38834,15 @@
       <c r="AX9" t="n">
         <v>0</v>
       </c>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
+      <c r="AY9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
       <c r="BB9" t="inlineStr">
         <is>
           <t>MATURE</t>
@@ -37671,7 +39015,7 @@
         <v>8531</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW10" t="n">
         <v>0</v>
@@ -37679,9 +39023,15 @@
       <c r="AX10" t="n">
         <v>0</v>
       </c>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="inlineStr"/>
+      <c r="AY10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
       <c r="BB10" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -37854,7 +39204,7 @@
         <v>3654</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW11" t="n">
         <v>0</v>
@@ -37862,9 +39212,15 @@
       <c r="AX11" t="n">
         <v>0</v>
       </c>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="inlineStr"/>
+      <c r="AY11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
       <c r="BB11" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -38033,7 +39389,7 @@
         <v>2837.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW12" t="n">
         <v>0</v>
@@ -38041,9 +39397,15 @@
       <c r="AX12" t="n">
         <v>0</v>
       </c>
-      <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr"/>
-      <c r="BA12" t="inlineStr"/>
+      <c r="AY12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
       <c r="BB12" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -38212,7 +39574,7 @@
         <v>4985</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
@@ -38220,9 +39582,15 @@
       <c r="AX13" t="n">
         <v>0</v>
       </c>
-      <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr"/>
-      <c r="BA13" t="inlineStr"/>
+      <c r="AY13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
       <c r="BB13" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -38391,7 +39759,7 @@
         <v>3000</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW14" t="n">
         <v>0</v>
@@ -38399,9 +39767,15 @@
       <c r="AX14" t="n">
         <v>0</v>
       </c>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr"/>
-      <c r="BA14" t="inlineStr"/>
+      <c r="AY14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
       <c r="BB14" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -38570,7 +39944,7 @@
         <v>4074</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
@@ -38578,9 +39952,15 @@
       <c r="AX15" t="n">
         <v>0</v>
       </c>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr"/>
-      <c r="BA15" t="inlineStr"/>
+      <c r="AY15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
       <c r="BB15" t="inlineStr">
         <is>
           <t>MATURE</t>
@@ -38749,7 +40129,7 @@
         <v>8059</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
@@ -38757,9 +40137,15 @@
       <c r="AX16" t="n">
         <v>0</v>
       </c>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr"/>
-      <c r="BA16" t="inlineStr"/>
+      <c r="AY16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
       <c r="BB16" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -38928,7 +40314,7 @@
         <v>1370.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW17" t="n">
         <v>0</v>
@@ -38936,9 +40322,15 @@
       <c r="AX17" t="n">
         <v>0</v>
       </c>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr"/>
-      <c r="BA17" t="inlineStr"/>
+      <c r="AY17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
       <c r="BB17" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -39107,7 +40499,7 @@
         <v>12040</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW18" t="n">
         <v>0</v>
@@ -39115,9 +40507,15 @@
       <c r="AX18" t="n">
         <v>0</v>
       </c>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr"/>
-      <c r="BA18" t="inlineStr"/>
+      <c r="AY18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
       <c r="BB18" t="inlineStr">
         <is>
           <t>MATURE</t>
@@ -39290,7 +40688,7 @@
         <v>6900</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW19" t="n">
         <v>0</v>
@@ -39298,9 +40696,15 @@
       <c r="AX19" t="n">
         <v>0</v>
       </c>
-      <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr"/>
-      <c r="BA19" t="inlineStr"/>
+      <c r="AY19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
       <c r="BB19" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -39469,7 +40873,7 @@
         <v>2141.5</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW20" t="n">
         <v>0</v>
@@ -39477,9 +40881,15 @@
       <c r="AX20" t="n">
         <v>0</v>
       </c>
-      <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="inlineStr"/>
-      <c r="BA20" t="inlineStr"/>
+      <c r="AY20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
       <c r="BB20" t="inlineStr">
         <is>
           <t>MATURE</t>
@@ -39937,9 +41347,15 @@
         <v>0</v>
       </c>
       <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
+      <c r="AY2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
       <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="inlineStr">
         <is>
@@ -40102,9 +41518,15 @@
         <v>0</v>
       </c>
       <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
+      <c r="AY3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr">
         <is>
@@ -40267,9 +41689,15 @@
         <v>0</v>
       </c>
       <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
+      <c r="AY4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr">
         <is>
@@ -40432,9 +41860,15 @@
         <v>0</v>
       </c>
       <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
+      <c r="AY5" t="n">
+        <v>64</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
       <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="inlineStr">
         <is>
@@ -40597,9 +42031,15 @@
         <v>0</v>
       </c>
       <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
+      <c r="AY6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr">
         <is>
@@ -40760,9 +42200,15 @@
         <v>0</v>
       </c>
       <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="inlineStr"/>
+      <c r="AY7" t="n">
+        <v>74</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
       <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="inlineStr">
         <is>
@@ -40925,9 +42371,15 @@
         <v>0</v>
       </c>
       <c r="AX8" t="inlineStr"/>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="inlineStr"/>
+      <c r="AY8" t="n">
+        <v>79</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr">
         <is>
@@ -41090,9 +42542,15 @@
         <v>0</v>
       </c>
       <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
+      <c r="AY9" t="n">
+        <v>118</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
       <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="inlineStr">
         <is>
@@ -41255,9 +42713,15 @@
         <v>0</v>
       </c>
       <c r="AX10" t="inlineStr"/>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="inlineStr"/>
+      <c r="AY10" t="n">
+        <v>122</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
       <c r="BB10" t="inlineStr"/>
       <c r="BC10" t="inlineStr">
         <is>
@@ -41418,9 +42882,15 @@
         <v>0</v>
       </c>
       <c r="AX11" t="inlineStr"/>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="inlineStr"/>
+      <c r="AY11" t="n">
+        <v>126</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr">
         <is>
@@ -41581,9 +43051,15 @@
         <v>0</v>
       </c>
       <c r="AX12" t="inlineStr"/>
-      <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr"/>
-      <c r="BA12" t="inlineStr"/>
+      <c r="AY12" t="n">
+        <v>130</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
       <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="inlineStr">
         <is>
@@ -41746,9 +43222,15 @@
         <v>0</v>
       </c>
       <c r="AX13" t="inlineStr"/>
-      <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr"/>
-      <c r="BA13" t="inlineStr"/>
+      <c r="AY13" t="n">
+        <v>141</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr">
         <is>
@@ -41907,9 +43389,15 @@
         <v>0</v>
       </c>
       <c r="AX14" t="inlineStr"/>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr"/>
-      <c r="BA14" t="inlineStr"/>
+      <c r="AY14" t="n">
+        <v>145</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr">
         <is>
@@ -42072,9 +43560,15 @@
         <v>0</v>
       </c>
       <c r="AX15" t="inlineStr"/>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr"/>
-      <c r="BA15" t="inlineStr"/>
+      <c r="AY15" t="n">
+        <v>148</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="inlineStr">
         <is>
@@ -42235,9 +43729,15 @@
         <v>0</v>
       </c>
       <c r="AX16" t="inlineStr"/>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr"/>
-      <c r="BA16" t="inlineStr"/>
+      <c r="AY16" t="n">
+        <v>152</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
       <c r="BB16" t="inlineStr"/>
       <c r="BC16" t="inlineStr">
         <is>
@@ -42400,9 +43900,15 @@
         <v>0</v>
       </c>
       <c r="AX17" t="inlineStr"/>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr"/>
-      <c r="BA17" t="inlineStr"/>
+      <c r="AY17" t="n">
+        <v>165</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
       <c r="BB17" t="inlineStr"/>
       <c r="BC17" t="inlineStr">
         <is>
@@ -42565,9 +44071,15 @@
         <v>0</v>
       </c>
       <c r="AX18" t="inlineStr"/>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr"/>
-      <c r="BA18" t="inlineStr"/>
+      <c r="AY18" t="n">
+        <v>172</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
       <c r="BB18" t="inlineStr"/>
       <c r="BC18" t="inlineStr">
         <is>
@@ -43027,7 +44539,7 @@
         <v>1841.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -43035,9 +44547,15 @@
       <c r="AX2" t="n">
         <v>0</v>
       </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
+      <c r="AY2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
       <c r="BB2" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -43204,9 +44722,15 @@
         <v>0</v>
       </c>
       <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
+      <c r="AY3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr">
         <is>
@@ -43369,9 +44893,15 @@
         <v>0</v>
       </c>
       <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
+      <c r="AY4" t="n">
+        <v>81</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr">
         <is>
@@ -43534,9 +45064,15 @@
         <v>0</v>
       </c>
       <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
+      <c r="AY5" t="n">
+        <v>47</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
       <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="inlineStr">
         <is>
@@ -43697,9 +45233,15 @@
         <v>0</v>
       </c>
       <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
+      <c r="AY6" t="n">
+        <v>186</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr">
         <is>
@@ -43862,9 +45404,15 @@
         <v>0</v>
       </c>
       <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="inlineStr"/>
+      <c r="AY7" t="n">
+        <v>67</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
       <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="inlineStr">
         <is>
@@ -44027,9 +45575,15 @@
         <v>0</v>
       </c>
       <c r="AX8" t="inlineStr"/>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="inlineStr"/>
+      <c r="AY8" t="n">
+        <v>140</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr">
         <is>
@@ -44198,7 +45752,7 @@
         <v>1734</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
@@ -44206,9 +45760,15 @@
       <c r="AX9" t="n">
         <v>0</v>
       </c>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
+      <c r="AY9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
       <c r="BB9" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -44375,9 +45935,15 @@
         <v>0</v>
       </c>
       <c r="AX10" t="inlineStr"/>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="inlineStr"/>
+      <c r="AY10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
       <c r="BB10" t="inlineStr"/>
       <c r="BC10" t="inlineStr">
         <is>
@@ -44540,9 +46106,15 @@
         <v>0</v>
       </c>
       <c r="AX11" t="inlineStr"/>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="inlineStr"/>
+      <c r="AY11" t="n">
+        <v>96</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr">
         <is>
@@ -44711,7 +46283,7 @@
         <v>3654</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW12" t="n">
         <v>0</v>
@@ -44719,9 +46291,15 @@
       <c r="AX12" t="n">
         <v>0</v>
       </c>
-      <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr"/>
-      <c r="BA12" t="inlineStr"/>
+      <c r="AY12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
       <c r="BB12" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -44888,9 +46466,15 @@
         <v>0</v>
       </c>
       <c r="AX13" t="inlineStr"/>
-      <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr"/>
-      <c r="BA13" t="inlineStr"/>
+      <c r="AY13" t="n">
+        <v>163</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr">
         <is>
@@ -45053,9 +46637,15 @@
         <v>0</v>
       </c>
       <c r="AX14" t="inlineStr"/>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr"/>
-      <c r="BA14" t="inlineStr"/>
+      <c r="AY14" t="n">
+        <v>92</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr">
         <is>
@@ -45224,7 +46814,7 @@
         <v>6900</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
@@ -45232,9 +46822,15 @@
       <c r="AX15" t="n">
         <v>0</v>
       </c>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr"/>
-      <c r="BA15" t="inlineStr"/>
+      <c r="AY15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
       <c r="BB15" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -45407,7 +47003,7 @@
         <v>8531</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
@@ -45415,9 +47011,15 @@
       <c r="AX16" t="n">
         <v>0</v>
       </c>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr"/>
-      <c r="BA16" t="inlineStr"/>
+      <c r="AY16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
       <c r="BB16" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -45584,9 +47186,15 @@
         <v>0</v>
       </c>
       <c r="AX17" t="inlineStr"/>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr"/>
-      <c r="BA17" t="inlineStr"/>
+      <c r="AY17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
       <c r="BB17" t="inlineStr"/>
       <c r="BC17" t="inlineStr">
         <is>
@@ -46046,7 +47654,7 @@
         <v>1734</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -46054,9 +47662,15 @@
       <c r="AX2" t="n">
         <v>0</v>
       </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
+      <c r="AY2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
       <c r="BB2" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -46225,7 +47839,7 @@
         <v>2081</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -46233,9 +47847,15 @@
       <c r="AX3" t="n">
         <v>0</v>
       </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
+      <c r="AY3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
       <c r="BB3" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -46404,7 +48024,7 @@
         <v>7647</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
@@ -46412,9 +48032,15 @@
       <c r="AX4" t="n">
         <v>0</v>
       </c>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
+      <c r="AY4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
       <c r="BB4" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -46587,7 +48213,7 @@
         <v>8531</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
@@ -46595,9 +48221,15 @@
       <c r="AX5" t="n">
         <v>0</v>
       </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
+      <c r="AY5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
       <c r="BB5" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -46770,7 +48402,7 @@
         <v>3654</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
@@ -46778,9 +48410,15 @@
       <c r="AX6" t="n">
         <v>0</v>
       </c>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
+      <c r="AY6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
       <c r="BB6" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -46949,7 +48587,7 @@
         <v>2837.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
@@ -46957,9 +48595,15 @@
       <c r="AX7" t="n">
         <v>0</v>
       </c>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="inlineStr"/>
+      <c r="AY7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
       <c r="BB7" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -47128,7 +48772,7 @@
         <v>4985</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
@@ -47136,9 +48780,15 @@
       <c r="AX8" t="n">
         <v>0</v>
       </c>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="inlineStr"/>
+      <c r="AY8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
       <c r="BB8" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -47307,7 +48957,7 @@
         <v>8059</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
@@ -47315,9 +48965,15 @@
       <c r="AX9" t="n">
         <v>0</v>
       </c>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
+      <c r="AY9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
       <c r="BB9" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -47486,7 +49142,7 @@
         <v>1370.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW10" t="n">
         <v>0</v>
@@ -47494,9 +49150,15 @@
       <c r="AX10" t="n">
         <v>0</v>
       </c>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="inlineStr"/>
+      <c r="AY10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
       <c r="BB10" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -47669,7 +49331,7 @@
         <v>6900</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW11" t="n">
         <v>0</v>
@@ -47677,9 +49339,15 @@
       <c r="AX11" t="n">
         <v>0</v>
       </c>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="inlineStr"/>
+      <c r="AY11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
       <c r="BB11" t="inlineStr">
         <is>
           <t>ACCELERATION</t>
@@ -48139,7 +49807,7 @@
         <v>1554</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -48147,9 +49815,15 @@
       <c r="AX2" t="n">
         <v>0</v>
       </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
+      <c r="AY2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
       <c r="BB2" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -48322,7 +49996,7 @@
         <v>1841.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -48330,9 +50004,15 @@
       <c r="AX3" t="n">
         <v>0</v>
       </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
+      <c r="AY3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
       <c r="BB3" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -48501,7 +50181,7 @@
         <v>1771</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
@@ -48509,9 +50189,15 @@
       <c r="AX4" t="n">
         <v>0</v>
       </c>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
+      <c r="AY4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
       <c r="BB4" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -48680,7 +50366,7 @@
         <v>497.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
@@ -48688,9 +50374,15 @@
       <c r="AX5" t="n">
         <v>0</v>
       </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
+      <c r="AY5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
       <c r="BB5" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -48859,7 +50551,7 @@
         <v>3000</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
@@ -48867,9 +50559,15 @@
       <c r="AX6" t="n">
         <v>0</v>
       </c>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
+      <c r="AY6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
       <c r="BB6" t="inlineStr">
         <is>
           <t>NEW</t>

--- a/reports/daily/nikkei225_ranking_ver7_20260818.xlsx
+++ b/reports/daily/nikkei225_ranking_ver7_20260818.xlsx
@@ -707,7 +707,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SUMITOMO MITSUI TRUST GP INC</t>
+          <t>三井住友トラストグループ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -860,7 +860,7 @@
         <v>1734</v>
       </c>
       <c r="AV2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -896,7 +896,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SUZUKI MOTOR CORP</t>
+          <t>スズキ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1045,7 +1045,7 @@
         <v>2081</v>
       </c>
       <c r="AV3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NOMURA HOLDINGS INC.</t>
+          <t>野村ホールディングス</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1230,7 +1230,7 @@
         <v>1554</v>
       </c>
       <c r="AV4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DAIICHI LIFE GROUP INC</t>
+          <t>第一生命ホールディングス</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1419,7 +1419,7 @@
         <v>1841.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DAIWA SECURITIES GROUP</t>
+          <t>大和証券グループ本社</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1604,7 +1604,7 @@
         <v>1771</v>
       </c>
       <c r="AV6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YOKOHAMA RUBBER CO</t>
+          <t>横浜ゴム</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1789,7 +1789,7 @@
         <v>7647</v>
       </c>
       <c r="AV7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LY CORPORATION</t>
+          <t>LINEヤフー</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1974,7 +1974,7 @@
         <v>497.9</v>
       </c>
       <c r="AV8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DIC CORPORATION</t>
+          <t>DIC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2159,7 +2159,7 @@
         <v>5495</v>
       </c>
       <c r="AV9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MIZUHO FINANCIAL GROUP</t>
+          <t>みずほフィナンシャルグループ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2348,7 +2348,7 @@
         <v>8531</v>
       </c>
       <c r="AV10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW10" t="n">
         <v>0</v>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MITSUBISHI UFJ FINANCIAL GROUP </t>
+          <t>三菱UFJフィナンシャル・グループ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2537,7 +2537,7 @@
         <v>3654</v>
       </c>
       <c r="AV11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW11" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CHIBA BANK</t>
+          <t>千葉銀行</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2722,7 +2722,7 @@
         <v>2837.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW12" t="n">
         <v>0</v>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MS&amp;AD INS GP HLDGS</t>
+          <t>MS&amp;ADインシュアランスグループホールディングス</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2907,7 +2907,7 @@
         <v>4985</v>
       </c>
       <c r="AV13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KIRIN HOLDINGS COMPANY LIMITED</t>
+          <t>キリンホールディングス</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3092,7 +3092,7 @@
         <v>3000</v>
       </c>
       <c r="AV14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW14" t="n">
         <v>0</v>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BRIDGESTONE CORP</t>
+          <t>ブリヂストン</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3277,7 +3277,7 @@
         <v>4074</v>
       </c>
       <c r="AV15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NISSAN CHEMICAL CORPORATION</t>
+          <t>日産化学</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3462,7 +3462,7 @@
         <v>8059</v>
       </c>
       <c r="AV16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IDEMITSU KOSAN CO.LTD</t>
+          <t>出光興産</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3647,7 +3647,7 @@
         <v>1370.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW17" t="n">
         <v>0</v>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>OTSUKA HLDGS CO LTD</t>
+          <t>大塚ホールディングス</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3832,7 +3832,7 @@
         <v>12040</v>
       </c>
       <c r="AV18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW18" t="n">
         <v>0</v>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SUMITOMO MITSUI FINANCIAL GROUP</t>
+          <t>三井住友フィナンシャルグループ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -4021,7 +4021,7 @@
         <v>6900</v>
       </c>
       <c r="AV19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW19" t="n">
         <v>0</v>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NICHIREI CORP</t>
+          <t>ニチレイ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4206,7 +4206,7 @@
         <v>2141.5</v>
       </c>
       <c r="AV20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW20" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FUKUOKA FINANCIAL GROUP INC.</t>
+          <t>ふくおかフィナンシャルグループ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ORIX CORPORATION</t>
+          <t>オリックス</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ASTELLAS PHARMA</t>
+          <t>アステラス製薬</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>OKUMA CORPORATION</t>
+          <t>オークマ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ADVANTEST CORP</t>
+          <t>アドバンテスト</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AJINOMOTO CO INC</t>
+          <t>味の素</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>KIKKOMAN CORP</t>
+          <t>キッコーマン</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RESONA HOLDINGS</t>
+          <t>りそなホールディングス</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JAPAN TOBACCO INC</t>
+          <t>日本たばこ産業（JT）</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NITTO DENKO CORP</t>
+          <t>日東電工</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DOWA HOLDINGS</t>
+          <t>DOWAホールディングス</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>T&amp;D HOLDINGS INC</t>
+          <t>T&amp;Dホールディングス</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TERUMO CORP</t>
+          <t>テルモ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>KYOCERA CORP</t>
+          <t>京セラ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ANA HOLDINGS INC</t>
+          <t>ANAホールディングス</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HITACHI CONSTRUCTION MACHINERY</t>
+          <t>日立建機</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JAPAN POST HLDGS CO LTD</t>
+          <t>日本郵政</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>KEISEI ELECTRIC RAILWAY CO</t>
+          <t>京成電鉄</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SEIKO EPSON CORP</t>
+          <t>セイコーエプソン</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SUMITOMO HEAVY INDUSTRIES</t>
+          <t>住友重機械工業</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>KYOWA KIRIN CO LTD</t>
+          <t>協和キリン</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CANON INC</t>
+          <t>キヤノン</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>KOMATSU</t>
+          <t>小松製作所</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>KONAMI GROUP CORPORATION</t>
+          <t>コナミグループ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JAPAN AIRLINES CO LTD</t>
+          <t>日本航空</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MATSUI SECURITIES CO</t>
+          <t>松井証券</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CREDIT SAISON CO</t>
+          <t>クレディセゾン</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NTT INC</t>
+          <t>NTT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>YAMAHA CORP</t>
+          <t>ヤマハ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -9111,7 +9111,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TOYOTA TSUSHO CORP</t>
+          <t>豊田通商</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NISSUI CORPORATION</t>
+          <t>ニッスイ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NIPPON EXPRESS HLDGS INC</t>
+          <t>NIPPON EXPRESSホールディングス</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TOKAI CARBON CO</t>
+          <t>東海カーボン</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MITSUI CHEMICALS INC</t>
+          <t>三井化学</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>YOKOHAMA FINANCIAL GROUP INC</t>
+          <t>コンコルディア・フィナンシャルグループ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TORAY INDUSTRIES INC</t>
+          <t>東レ</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RICOH CO</t>
+          <t>リコー</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -10445,7 +10445,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SUMITOMO METAL MINING CO</t>
+          <t>住友金属鉱山</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -10612,7 +10612,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SUMITOMO CORP</t>
+          <t>住友商事</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>KAO CORP</t>
+          <t>花王</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CITIZEN WATCH CO LTD</t>
+          <t>シチズン時計</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ENEOS HOLDINGS INC</t>
+          <t>ENEOSホールディングス</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -11278,7 +11278,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HONDA MOTOR CO</t>
+          <t>本田技研工業</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PANASONIC HOLDINGS CORP</t>
+          <t>パナソニック ホールディングス</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SONY GROUP CORPORATION</t>
+          <t>ソニーグループ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SUMITOMO OSAKA CEMENT CO</t>
+          <t>住友大阪セメント</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -11944,7 +11944,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>KURARAY CO</t>
+          <t>クラレ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>KDDI CORPORATION</t>
+          <t>KDDI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MITSUBISHI CHEMICAL GROUP CORP</t>
+          <t>三菱ケミカルグループ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -12447,7 +12447,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>OMRON CORP</t>
+          <t>オムロン</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FUJI ELECTRIC CO. LTD.</t>
+          <t>富士電機</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BANDAI NAMCO HOLDINGS INC</t>
+          <t>バンダイナムコホールディングス</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -12952,7 +12952,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>RECRUIT HOLDINGS CO LTD</t>
+          <t>リクルートホールディングス</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HOYA CORP</t>
+          <t>HOYA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>KEYENCE CORP</t>
+          <t>キーエンス</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -13455,7 +13455,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>IHI CORPORATION</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -13491,7 +13491,7 @@
         <v>5.2</v>
       </c>
       <c r="K76" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="L76" t="n">
         <v>33.4</v>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NIPPON YUSEN KABUSHIKI KAISHA</t>
+          <t>日本郵船</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -13789,7 +13789,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>UBE CORPORATION</t>
+          <t>UBE</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TOYOTA MOTOR CORP</t>
+          <t>トヨタ自動車</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -14123,7 +14123,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NIDEC CORPORATION</t>
+          <t>ニデック</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>UNITIKA LTD</t>
+          <t>ユニチカ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -14459,7 +14459,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SOFTBANK CORP.</t>
+          <t>ソフトバンク</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TOBU RAILWAY CO</t>
+          <t>東武鉄道</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -14797,7 +14797,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TOPPAN HOLDINGS INC</t>
+          <t>TOPPANホールディングス</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -14964,7 +14964,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>KANSAI ELECTRIC POWER CO INC</t>
+          <t>関西電力</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -15131,7 +15131,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DAI NIPPON PRINTING CO</t>
+          <t>大日本印刷</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -15298,7 +15298,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JTEKT CORPORATION</t>
+          <t>ジェイテクト</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -15465,7 +15465,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MITSUI O.S.K. LINES LTD</t>
+          <t>商船三井</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>RESONAC HOLDINGS CORPORATION</t>
+          <t>レゾナック・ホールディングス</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TAIHEIYO CEMENT CORP</t>
+          <t>太平洋セメント</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JFE HOLDINGS INC</t>
+          <t>JFEホールディングス</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -16133,7 +16133,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SAPPORO BREWERIES LTD</t>
+          <t>サッポロホールディングス</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -16298,7 +16298,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ITOCHU CORP</t>
+          <t>伊藤忠商事</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EISAI CO LTD</t>
+          <t>エーザイ</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -16636,7 +16636,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MITSUBISHI MATERIALS CORP</t>
+          <t>三菱マテリアル</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -16801,7 +16801,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SHISEIDO COMPANY LIMITED</t>
+          <t>資生堂</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -16966,7 +16966,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MITSUBISHI CORP</t>
+          <t>三菱商事</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -17137,7 +17137,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TAKASHIMAYA CO</t>
+          <t>高島屋</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -17302,7 +17302,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MAZDA MOTOR CORP</t>
+          <t>マツダ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -17467,7 +17467,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>INPEX CORPORATION</t>
+          <t>INPEX</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -17634,7 +17634,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>HASEKO CORPORATION</t>
+          <t>長谷工コーポレーション</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -17801,7 +17801,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TDK CORP</t>
+          <t>TDK</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -17968,7 +17968,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>OLYMPUS CORPORATION</t>
+          <t>オリンパス</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -18135,7 +18135,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>COMSYS HOLDINGS CORP</t>
+          <t>コムシスホールディングス</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -18302,7 +18302,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>FUJIKURA</t>
+          <t>フジクラ</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -18465,7 +18465,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SEKISUI HOUSE</t>
+          <t>積水ハウス</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -18632,7 +18632,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>NIPPON STEEL CORPORATION</t>
+          <t>日本製鉄</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -18797,7 +18797,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>KAWASAKI HEAVY INDUSTRIES</t>
+          <t>川崎重工業</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -18964,7 +18964,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>KOBE STEEL</t>
+          <t>神戸製鋼所</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -19127,7 +19127,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MITSUBISHI LOGISTICS CORP</t>
+          <t>三菱倉庫</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -19294,7 +19294,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>DAIWA HOUSE INDUSTRY CO</t>
+          <t>大和ハウス工業</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -19461,7 +19461,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>OJI HOLDINGS CORP</t>
+          <t>王子ホールディングス</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -19626,7 +19626,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MEIJI HOLDINGS CO LTD</t>
+          <t>明治ホールディングス</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -19793,7 +19793,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>KUBOTA CORP</t>
+          <t>クボタ</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -19960,7 +19960,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SHIONOGI &amp; CO</t>
+          <t>塩野義製薬</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -20127,7 +20127,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TOKYO TATEMONO CO</t>
+          <t>東京建物</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -20294,7 +20294,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TOYOBO CO</t>
+          <t>東洋紡</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -20461,7 +20461,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>NTN CORP</t>
+          <t>NTN</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>NEC CORP</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -20799,7 +20799,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>CENTRAL JAPAN RAILWAY CO</t>
+          <t>JR東海</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -20966,7 +20966,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SUMITOMO CHEMICAL COMPANY</t>
+          <t>住友化学</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>FURUKAWA ELECTRIC CO</t>
+          <t>古河電気工業</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -21298,7 +21298,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SOFTBANK GROUP CORP</t>
+          <t>ソフトバンクグループ</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -21469,7 +21469,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>MARUI GROUP CO LTD</t>
+          <t>丸井グループ</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -21636,7 +21636,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>KAWASAKI KISEN KAISHA</t>
+          <t>川崎汽船</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -21803,7 +21803,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>JGC HOLDINGS CORPORATION</t>
+          <t>日揮ホールディングス</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -21970,7 +21970,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC CORP</t>
+          <t>三菱電機</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -22139,7 +22139,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>FAST RETAILING CO LTD</t>
+          <t>ファーストリテイリング</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -22306,7 +22306,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ASAHI KASEI CORP</t>
+          <t>旭化成</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -22473,7 +22473,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>NSK</t>
+          <t>日本精工</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -22640,7 +22640,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>HITACHI</t>
+          <t>日立製作所</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -22809,7 +22809,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>JAPAN EXCHANGE GROUP</t>
+          <t>日本取引所グループ</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -22970,7 +22970,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>RYOHIN KEIKAKU CO</t>
+          <t>良品計画</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -23135,7 +23135,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>TAKEDA PHARMACEUTICAL CO LTD</t>
+          <t>武田薬品工業</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -23300,7 +23300,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>CHUBU ELECTRIC POWER CO INC</t>
+          <t>中部電力</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -23467,7 +23467,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ODAKYU ELECTRIC RAILWAY CO</t>
+          <t>小田急電鉄</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -23634,7 +23634,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ALPS ALPINE CO LTD</t>
+          <t>アルプスアルパイン</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -23799,7 +23799,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>NISSHIN SEIFUN GROUP INC</t>
+          <t>日清製粉グループ本社</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -23966,7 +23966,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ASAHI GROUP HLDGS</t>
+          <t>アサヒグループホールディングス</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SEVEN &amp; I HOLDINGS CO LTD</t>
+          <t>セブン＆アイ・ホールディングス</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -24300,7 +24300,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MITSUI &amp; CO</t>
+          <t>三井物産</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -24471,7 +24471,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>TOKYO ELECTRON</t>
+          <t>東京エレクトロン</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -24642,7 +24642,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>NGK CORP</t>
+          <t>日本ガイシ</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -24809,7 +24809,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>NITORI HOLDINGS CO LTD</t>
+          <t>ニトリホールディングス</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -24976,7 +24976,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MITSUBISHI HEAVY INDUSTRIES</t>
+          <t>三菱重工業</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -25143,7 +25143,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>KIOXIA HOLDINGS CORPORATION</t>
+          <t>キオクシアホールディングス</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -25310,7 +25310,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>NEXON CO LTD</t>
+          <t>ネクソン</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -25477,7 +25477,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>DENA CO LTD</t>
+          <t>ディー・エヌ・エー</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -25644,7 +25644,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>MURATA MANUFACTURING CO</t>
+          <t>村田製作所</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -25815,7 +25815,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>TEIJIN LTD</t>
+          <t>帝人</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -25978,7 +25978,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>KEIO CORPORATION</t>
+          <t>京王電鉄</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -26145,7 +26145,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>TOSOH CORP</t>
+          <t>東ソー</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -26310,7 +26310,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>RENESAS ELECTRONICS CORP</t>
+          <t>ルネサスエレクトロニクス</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -26479,7 +26479,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SUMITOMO ELECTRIC INDUSTRIES</t>
+          <t>住友電気工業</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -26646,7 +26646,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>DAIICHI SANKYO COMPANY LIMITED</t>
+          <t>第一三共</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -26813,7 +26813,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>AMADA CO LTD</t>
+          <t>アマダ</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -26978,7 +26978,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>KANADEVIA CORPORATION</t>
+          <t>カナデビア</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -27141,7 +27141,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PAN PACIFIC INTL HLDGS CORP</t>
+          <t>パン・パシフィック・インターナショナルホールディングス</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -27306,7 +27306,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>DENSO CORP</t>
+          <t>デンソー</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -27473,7 +27473,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>OBAYASHI CORP</t>
+          <t>大林組</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -27640,7 +27640,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>WEST JAPAN RAILWAY CO</t>
+          <t>JR西日本</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -27807,7 +27807,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>TOHO CO LTD</t>
+          <t>東宝</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -27974,7 +27974,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>SUMITOMO PHARMA CO LTD</t>
+          <t>住友ファーマ</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -28139,7 +28139,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>MARUBENI CORP</t>
+          <t>丸紅</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -28310,7 +28310,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>J FRONT RETAILING CO LTD</t>
+          <t>J.フロント リテイリング</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -28477,7 +28477,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>FUJITSU</t>
+          <t>富士通</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -28648,7 +28648,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SHIMIZU CORP</t>
+          <t>清水建設</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -28815,7 +28815,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ISUZU MOTORS</t>
+          <t>いすゞ自動車</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -28982,7 +28982,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ISETAN MITSUKOSHI HOLDINGS LTD</t>
+          <t>三越伊勢丹ホールディングス</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -29147,7 +29147,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>EBARA CORP</t>
+          <t>荏原製作所</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -29314,7 +29314,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>NH FOODS LTD</t>
+          <t>日本ハム</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -29481,7 +29481,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ZOZO INC</t>
+          <t>ZOZO</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -29648,7 +29648,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>SHIN-ETSU CHEMICAL CO</t>
+          <t>信越化学工業</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -29819,7 +29819,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>MITSUBISHI MOTOR CORP</t>
+          <t>三菱自動車工業</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -29986,7 +29986,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>TOKYU FUDOSAN HOLDINGS CORPORAT</t>
+          <t>東急不動産ホールディングス</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -30153,7 +30153,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>DENTSU GROUP INC</t>
+          <t>電通グループ</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -30310,7 +30310,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>SUMCO CORPORATION</t>
+          <t>SUMCO</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -30473,7 +30473,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>CHUGAI PHARMACEUTICAL CO</t>
+          <t>中外製薬</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -30640,7 +30640,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>TOKYO GAS CO</t>
+          <t>東京ガス</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -30807,7 +30807,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SUBARU CORPORATION</t>
+          <t>SUBARU</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -30974,7 +30974,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SCREEN HOLDINGS CO LTD</t>
+          <t>SCREENホールディングス</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -31141,7 +31141,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>NINTENDO CO LTD</t>
+          <t>任天堂</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -31306,7 +31306,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>YAMATO HOLDINGS CO LTD</t>
+          <t>ヤマトホールディングス</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -31471,7 +31471,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>SECOM CO</t>
+          <t>セコム</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -31638,7 +31638,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>AGC INC</t>
+          <t>AGC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -31803,7 +31803,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>MITSUBISHI ESTATE CO</t>
+          <t>三菱地所</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -31970,7 +31970,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>TOKIO MARINE HOLDINGS INC</t>
+          <t>東京海上ホールディングス</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -32139,7 +32139,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>M3 INC</t>
+          <t>エムスリー</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -32300,7 +32300,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>OSAKA GAS CO</t>
+          <t>大阪ガス</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -32467,7 +32467,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>TOKYO METRO CO LTD</t>
+          <t>東京地下鉄</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -32632,7 +32632,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>YOKOGAWA ELECTRIC CORP</t>
+          <t>横河電機</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -32797,7 +32797,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>SHARP CORP</t>
+          <t>シャープ</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -32962,7 +32962,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>TOKYU CORP</t>
+          <t>東急</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -33127,7 +33127,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>TAIYO YUDEN CO LTD</t>
+          <t>太陽誘電</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -33292,7 +33292,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>AEON CO LTD</t>
+          <t>イオン</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -33457,7 +33457,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>DAIKIN INDUSTRIES</t>
+          <t>ダイキン工業</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -33620,7 +33620,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>TOKYO ELEC POWER CO HLDGS INC</t>
+          <t>東京電力ホールディングス</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -33781,7 +33781,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>DENKA COMPANY LIMITED</t>
+          <t>デンカ</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -33944,7 +33944,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>EAST JAPAN RAILWAY CO</t>
+          <t>JR東日本</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -34111,7 +34111,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>NIKON CORP</t>
+          <t>ニコン</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -34276,7 +34276,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>TAISEI CORP</t>
+          <t>大成建設</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -34441,7 +34441,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>CYBER AGENT</t>
+          <t>サイバーエージェント</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -34608,7 +34608,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>MITSUI FUDOSAN</t>
+          <t>三井不動産</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -34775,7 +34775,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>MITSUI KINZOKU CO LTD</t>
+          <t>三井金属</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -34940,7 +34940,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>LASERTEC CORP</t>
+          <t>レーザーテック</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -34976,7 +34976,7 @@
         <v>33.9</v>
       </c>
       <c r="K205" t="n">
-        <v>14.7</v>
+        <v>13.4</v>
       </c>
       <c r="L205" t="n">
         <v>33.9</v>
@@ -35107,7 +35107,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>TOTO LTD</t>
+          <t>TOTO</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -35274,7 +35274,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>FUJIFILM HOLDINGS CORPORATION</t>
+          <t>富士フイルムホールディングス</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -35441,7 +35441,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>TREND MICRO INC</t>
+          <t>トレンドマイクロ</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -35608,7 +35608,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>SUMITOMO REALTY &amp; DEVELOPMENT C</t>
+          <t>住友不動産</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -35771,7 +35771,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>FANUC CORPORATION</t>
+          <t>ファナック</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -35938,7 +35938,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>KAJIMA CORP</t>
+          <t>鹿島建設</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -36103,7 +36103,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>NISSAN MOTOR CO</t>
+          <t>日産自動車</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -36264,7 +36264,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>TOKUYAMA CORP</t>
+          <t>トクヤマ</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -36425,7 +36425,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>NIPPON ELECTRIC GLASS</t>
+          <t>日本電気硝子</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -36590,7 +36590,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>RAKUTEN GROUP INC</t>
+          <t>楽天グループ</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -36751,7 +36751,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>YASKAWA ELECTRIC CORP</t>
+          <t>安川電機</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -36918,7 +36918,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>SOCIONEXT INC</t>
+          <t>ソシオネクスト</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -37374,7 +37374,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SUMITOMO MITSUI TRUST GP INC</t>
+          <t>三井住友トラストグループ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -37527,7 +37527,7 @@
         <v>1734</v>
       </c>
       <c r="AV2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -37563,7 +37563,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SUZUKI MOTOR CORP</t>
+          <t>スズキ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -37712,7 +37712,7 @@
         <v>2081</v>
       </c>
       <c r="AV3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -37748,7 +37748,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NOMURA HOLDINGS INC.</t>
+          <t>野村ホールディングス</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -37897,7 +37897,7 @@
         <v>1554</v>
       </c>
       <c r="AV4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
@@ -37933,7 +37933,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DAIICHI LIFE GROUP INC</t>
+          <t>第一生命ホールディングス</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -38086,7 +38086,7 @@
         <v>1841.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
@@ -38122,7 +38122,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DAIWA SECURITIES GROUP</t>
+          <t>大和証券グループ本社</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -38271,7 +38271,7 @@
         <v>1771</v>
       </c>
       <c r="AV6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
@@ -38307,7 +38307,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YOKOHAMA RUBBER CO</t>
+          <t>横浜ゴム</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -38456,7 +38456,7 @@
         <v>7647</v>
       </c>
       <c r="AV7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
@@ -38492,7 +38492,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LY CORPORATION</t>
+          <t>LINEヤフー</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -38641,7 +38641,7 @@
         <v>497.9</v>
       </c>
       <c r="AV8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
@@ -38677,7 +38677,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DIC CORPORATION</t>
+          <t>DIC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -38826,7 +38826,7 @@
         <v>5495</v>
       </c>
       <c r="AV9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
@@ -38862,7 +38862,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MIZUHO FINANCIAL GROUP</t>
+          <t>みずほフィナンシャルグループ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -39015,7 +39015,7 @@
         <v>8531</v>
       </c>
       <c r="AV10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW10" t="n">
         <v>0</v>
@@ -39051,7 +39051,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MITSUBISHI UFJ FINANCIAL GROUP </t>
+          <t>三菱UFJフィナンシャル・グループ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -39204,7 +39204,7 @@
         <v>3654</v>
       </c>
       <c r="AV11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW11" t="n">
         <v>0</v>
@@ -39240,7 +39240,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CHIBA BANK</t>
+          <t>千葉銀行</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -39389,7 +39389,7 @@
         <v>2837.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW12" t="n">
         <v>0</v>
@@ -39425,7 +39425,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MS&amp;AD INS GP HLDGS</t>
+          <t>MS&amp;ADインシュアランスグループホールディングス</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -39574,7 +39574,7 @@
         <v>4985</v>
       </c>
       <c r="AV13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
@@ -39610,7 +39610,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KIRIN HOLDINGS COMPANY LIMITED</t>
+          <t>キリンホールディングス</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -39759,7 +39759,7 @@
         <v>3000</v>
       </c>
       <c r="AV14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW14" t="n">
         <v>0</v>
@@ -39795,7 +39795,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BRIDGESTONE CORP</t>
+          <t>ブリヂストン</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -39944,7 +39944,7 @@
         <v>4074</v>
       </c>
       <c r="AV15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
@@ -39980,7 +39980,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NISSAN CHEMICAL CORPORATION</t>
+          <t>日産化学</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -40129,7 +40129,7 @@
         <v>8059</v>
       </c>
       <c r="AV16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
@@ -40165,7 +40165,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IDEMITSU KOSAN CO.LTD</t>
+          <t>出光興産</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -40314,7 +40314,7 @@
         <v>1370.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW17" t="n">
         <v>0</v>
@@ -40350,7 +40350,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>OTSUKA HLDGS CO LTD</t>
+          <t>大塚ホールディングス</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -40499,7 +40499,7 @@
         <v>12040</v>
       </c>
       <c r="AV18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW18" t="n">
         <v>0</v>
@@ -40535,7 +40535,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SUMITOMO MITSUI FINANCIAL GROUP</t>
+          <t>三井住友フィナンシャルグループ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -40688,7 +40688,7 @@
         <v>6900</v>
       </c>
       <c r="AV19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW19" t="n">
         <v>0</v>
@@ -40724,7 +40724,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NICHIREI CORP</t>
+          <t>ニチレイ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -40873,7 +40873,7 @@
         <v>2141.5</v>
       </c>
       <c r="AV20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW20" t="n">
         <v>0</v>
@@ -41200,7 +41200,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ADVANTEST CORP</t>
+          <t>アドバンテスト</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -41371,7 +41371,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NITTO DENKO CORP</t>
+          <t>日東電工</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -41542,7 +41542,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SEIKO EPSON CORP</t>
+          <t>セイコーエプソン</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -41713,7 +41713,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SONY GROUP CORPORATION</t>
+          <t>ソニーグループ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -41884,7 +41884,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FUJI ELECTRIC CO. LTD.</t>
+          <t>富士電機</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -42055,7 +42055,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KEYENCE CORP</t>
+          <t>キーエンス</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -42224,7 +42224,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NIDEC CORPORATION</t>
+          <t>ニデック</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -42395,7 +42395,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NEC CORP</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -42566,7 +42566,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SOFTBANK GROUP CORP</t>
+          <t>ソフトバンクグループ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -42737,7 +42737,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC CORP</t>
+          <t>三菱電機</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -42906,7 +42906,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HITACHI</t>
+          <t>日立製作所</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -43075,7 +43075,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TOKYO ELECTRON</t>
+          <t>東京エレクトロン</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -43246,7 +43246,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KIOXIA HOLDINGS CORPORATION</t>
+          <t>キオクシアホールディングス</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -43413,7 +43413,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MURATA MANUFACTURING CO</t>
+          <t>村田製作所</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -43584,7 +43584,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RENESAS ELECTRONICS CORP</t>
+          <t>ルネサスエレクトロニクス</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -43753,7 +43753,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FUJITSU</t>
+          <t>富士通</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -43924,7 +43924,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SHIN-ETSU CHEMICAL CO</t>
+          <t>信越化学工業</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -44386,7 +44386,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DAIICHI LIFE GROUP INC</t>
+          <t>第一生命ホールディングス</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -44539,7 +44539,7 @@
         <v>1841.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -44575,7 +44575,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JAPAN TOBACCO INC</t>
+          <t>日本たばこ産業（JT）</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -44746,7 +44746,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SOFTBANK CORP.</t>
+          <t>ソフトバンク</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -44917,7 +44917,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NTT INC</t>
+          <t>NTT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -45088,7 +45088,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TOKIO MARINE HOLDINGS INC</t>
+          <t>東京海上ホールディングス</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -45257,7 +45257,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KDDI CORPORATION</t>
+          <t>KDDI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -45428,7 +45428,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MITSUI &amp; CO</t>
+          <t>三井物産</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -45599,7 +45599,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SUMITOMO MITSUI TRUST GP INC</t>
+          <t>三井住友トラストグループ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -45752,7 +45752,7 @@
         <v>1734</v>
       </c>
       <c r="AV9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
@@ -45788,7 +45788,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ORIX CORPORATION</t>
+          <t>オリックス</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -45959,7 +45959,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MITSUBISHI CORP</t>
+          <t>三菱商事</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -46130,7 +46130,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MITSUBISHI UFJ FINANCIAL GROUP </t>
+          <t>三菱UFJフィナンシャル・グループ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -46283,7 +46283,7 @@
         <v>3654</v>
       </c>
       <c r="AV12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW12" t="n">
         <v>0</v>
@@ -46319,7 +46319,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MARUBENI CORP</t>
+          <t>丸紅</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -46490,7 +46490,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ITOCHU CORP</t>
+          <t>伊藤忠商事</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -46661,7 +46661,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SUMITOMO MITSUI FINANCIAL GROUP</t>
+          <t>三井住友フィナンシャルグループ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -46814,7 +46814,7 @@
         <v>6900</v>
       </c>
       <c r="AV15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
@@ -46850,7 +46850,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIZUHO FINANCIAL GROUP</t>
+          <t>みずほフィナンシャルグループ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -47003,7 +47003,7 @@
         <v>8531</v>
       </c>
       <c r="AV16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
@@ -47039,7 +47039,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RESONA HOLDINGS</t>
+          <t>りそなホールディングス</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -47501,7 +47501,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SUMITOMO MITSUI TRUST GP INC</t>
+          <t>三井住友トラストグループ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -47654,7 +47654,7 @@
         <v>1734</v>
       </c>
       <c r="AV2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -47690,7 +47690,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SUZUKI MOTOR CORP</t>
+          <t>スズキ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -47839,7 +47839,7 @@
         <v>2081</v>
       </c>
       <c r="AV3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -47875,7 +47875,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>YOKOHAMA RUBBER CO</t>
+          <t>横浜ゴム</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -48024,7 +48024,7 @@
         <v>7647</v>
       </c>
       <c r="AV4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
@@ -48060,7 +48060,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MIZUHO FINANCIAL GROUP</t>
+          <t>みずほフィナンシャルグループ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -48213,7 +48213,7 @@
         <v>8531</v>
       </c>
       <c r="AV5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
@@ -48249,7 +48249,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MITSUBISHI UFJ FINANCIAL GROUP </t>
+          <t>三菱UFJフィナンシャル・グループ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -48402,7 +48402,7 @@
         <v>3654</v>
       </c>
       <c r="AV6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
@@ -48438,7 +48438,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CHIBA BANK</t>
+          <t>千葉銀行</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -48587,7 +48587,7 @@
         <v>2837.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
@@ -48623,7 +48623,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MS&amp;AD INS GP HLDGS</t>
+          <t>MS&amp;ADインシュアランスグループホールディングス</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -48772,7 +48772,7 @@
         <v>4985</v>
       </c>
       <c r="AV8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
@@ -48808,7 +48808,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NISSAN CHEMICAL CORPORATION</t>
+          <t>日産化学</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -48957,7 +48957,7 @@
         <v>8059</v>
       </c>
       <c r="AV9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
@@ -48993,7 +48993,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IDEMITSU KOSAN CO.LTD</t>
+          <t>出光興産</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -49142,7 +49142,7 @@
         <v>1370.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW10" t="n">
         <v>0</v>
@@ -49178,7 +49178,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SUMITOMO MITSUI FINANCIAL GROUP</t>
+          <t>三井住友フィナンシャルグループ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -49331,7 +49331,7 @@
         <v>6900</v>
       </c>
       <c r="AV11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW11" t="n">
         <v>0</v>
@@ -49658,7 +49658,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NOMURA HOLDINGS INC.</t>
+          <t>野村ホールディングス</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -49807,7 +49807,7 @@
         <v>1554</v>
       </c>
       <c r="AV2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -49843,7 +49843,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DAIICHI LIFE GROUP INC</t>
+          <t>第一生命ホールディングス</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -49996,7 +49996,7 @@
         <v>1841.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -50032,7 +50032,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DAIWA SECURITIES GROUP</t>
+          <t>大和証券グループ本社</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -50181,7 +50181,7 @@
         <v>1771</v>
       </c>
       <c r="AV4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
@@ -50217,7 +50217,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LY CORPORATION</t>
+          <t>LINEヤフー</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -50366,7 +50366,7 @@
         <v>497.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
@@ -50402,7 +50402,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KIRIN HOLDINGS COMPANY LIMITED</t>
+          <t>キリンホールディングス</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -50551,7 +50551,7 @@
         <v>3000</v>
       </c>
       <c r="AV6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
